--- a/DNP3/dnp3_capture_with_predictions.xlsx
+++ b/DNP3/dnp3_capture_with_predictions.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP61"/>
+  <dimension ref="A1:AP59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1781634397.382902</v>
+        <v>1781635912.649999</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>128</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>20003</v>
@@ -700,10 +700,10 @@
         <v>24</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>25584</v>
+        <v>29127</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35aeece013c02063c03063c0406773c</t>
+          <t>056411c401000200c35acece013c02063c03063c040644cb</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="n">
@@ -768,19 +768,19 @@
         </is>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.1590016842903675</v>
+        <v>0.1589473031231944</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.2024917598337787</v>
+        <v>0.2025790221881318</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.2930397021903922</v>
+        <v>0.2933037558894979</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.222228494000474</v>
+        <v>0.2220386482898196</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.1232383596849877</v>
+        <v>0.1231312705093563</v>
       </c>
     </row>
     <row r="3">
@@ -793,13 +793,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1781634397.635288</v>
+        <v>1781635912.773724</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.2523860931396484</v>
+        <v>0.1237251758575439</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.2523860931396484</v>
+        <v>0.1237251758575439</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>61</v>
@@ -829,7 +829,7 @@
         <v>20003</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>17</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>44886</v>
+        <v>33416</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.2523860931396484</v>
+        <v>0.1237251758575439</v>
       </c>
       <c r="U3" s="2" t="b">
         <v>1</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0efce81000037ad</t>
+          <t>05640a440200010010f0cfce8100006ab5</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="n">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.2284854263646152</v>
+        <v>0.2282145898787095</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.3323788705933914</v>
+        <v>0.3327438040946213</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.175389977647455</v>
+        <v>0.1754794513524278</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.1413525797763212</v>
+        <v>0.1413186656283982</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.1223931456182171</v>
+        <v>0.122243489045843</v>
       </c>
     </row>
     <row r="4">
@@ -931,13 +931,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1781634398.423298</v>
+        <v>1781635913.698105</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.040395975112915</v>
+        <v>1.04810619354248</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.7880098819732666</v>
+        <v>0.9243810176849365</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>68</v>
@@ -964,7 +964,7 @@
         <v>128</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>20003</v>
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>47932</v>
+        <v>34871</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.7880098819732666</v>
+        <v>0.9243810176849365</v>
       </c>
       <c r="U4" s="2" t="b">
         <v>1</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35aefcf013c02063c03063c04061ec6</t>
+          <t>056411c401000200c35acfcf013c02063c03063c04062d31</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="n">
@@ -1044,19 +1044,19 @@
         </is>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.1590017240758264</v>
+        <v>0.1589473381789431</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.2024915656456852</v>
+        <v>0.202578816970048</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.2930393142463484</v>
+        <v>0.2933033327664394</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.2222291555356629</v>
+        <v>0.2220393684469446</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.1232382404964771</v>
+        <v>0.1231311436376248</v>
       </c>
     </row>
     <row r="5">
@@ -1069,13 +1069,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1781634398.451127</v>
+        <v>1781635913.973298</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.068225145339966</v>
+        <v>1.323299169540405</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.02782917022705078</v>
+        <v>0.2751929759979248</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>61</v>
@@ -1105,7 +1105,7 @@
         <v>20003</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>24</v>
@@ -1114,13 +1114,13 @@
         <v>17</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>57933</v>
+        <v>54653</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.02782917022705078</v>
+        <v>0.2751929759979248</v>
       </c>
       <c r="U5" s="2" t="b">
         <v>1</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f0cf8100001679</t>
+          <t>05640a440200010010f0d0cf8100004b61</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="n">
@@ -1182,19 +1182,19 @@
         </is>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.228485775506305</v>
+        <v>0.2282151014687555</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.3323786612822373</v>
+        <v>0.3327434703135523</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.1753898864427914</v>
+        <v>0.1754792970544929</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.141352585800338</v>
+        <v>0.14131873828149</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.1223930909683285</v>
+        <v>0.1222433928817092</v>
       </c>
     </row>
     <row r="6">
@@ -1207,13 +1207,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1781634399.465998</v>
+        <v>1781635914.727573</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.083096027374268</v>
+        <v>2.077574014663696</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1.014870882034302</v>
+        <v>0.754274845123291</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>68</v>
@@ -1240,7 +1240,7 @@
         <v>128</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>20003</v>
@@ -1252,13 +1252,13 @@
         <v>24</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>20686</v>
+        <v>63584</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>1.014870882034302</v>
+        <v>0.754274845123291</v>
       </c>
       <c r="U6" s="2" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af0c0013c02063c03063c0406881a</t>
+          <t>056411c401000200c35ad0c0013c02063c03063c0406bbed</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
@@ -1320,19 +1320,19 @@
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.159001793068644</v>
+        <v>0.1589474231476581</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.2024914143059694</v>
+        <v>0.2025786958318671</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.293039045371601</v>
+        <v>0.2933031609964231</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.2222295904526193</v>
+        <v>0.2220396381795585</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.1232381568011664</v>
+        <v>0.1231310818444934</v>
       </c>
     </row>
     <row r="7">
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1781634399.663799</v>
+        <v>1781635914.919476</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2.28089714050293</v>
+        <v>2.269477128982544</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1978011131286621</v>
+        <v>0.1919031143188477</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>61</v>
@@ -1381,7 +1381,7 @@
         <v>20003</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>24</v>
@@ -1390,13 +1390,13 @@
         <v>17</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>57588</v>
+        <v>54438</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.1978011131286621</v>
+        <v>0.1919031143188477</v>
       </c>
       <c r="U7" s="2" t="b">
         <v>1</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f1c08100005579</t>
+          <t>05640a440200010010f0d1c08100000861</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="n">
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.228486292475297</v>
+        <v>0.2282155056958504</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.3323783246173846</v>
+        <v>0.33274321855336</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.1753897295674856</v>
+        <v>0.1754791836172614</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.1413526606057127</v>
+        <v>0.1413187686318065</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.1223929927341201</v>
+        <v>0.1222433235017215</v>
       </c>
     </row>
     <row r="8">
@@ -1483,13 +1483,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1781634400.516071</v>
+        <v>1781635915.762128</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3.133169174194336</v>
+        <v>3.112129211425781</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8522720336914062</v>
+        <v>0.8426520824432373</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>68</v>
@@ -1516,7 +1516,7 @@
         <v>128</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>20003</v>
@@ -1528,13 +1528,13 @@
         <v>24</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>62941</v>
+        <v>57612</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.8522720336914062</v>
+        <v>0.8426520824432373</v>
       </c>
       <c r="U8" s="2" t="b">
         <v>1</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af1c1013c02063c03063c0406e1e0</t>
+          <t>056411c401000200c35ad1c1013c02063c03063c0406d217</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
@@ -1596,19 +1596,19 @@
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.1590018787324681</v>
+        <v>0.1589474975099892</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>0.2024912900439454</v>
+        <v>0.2025785552823367</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.2930388684979514</v>
+        <v>0.293302926761489</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>0.2222298697707919</v>
+        <v>0.2220400145845226</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>0.1232380929548431</v>
+        <v>0.1231310058616625</v>
       </c>
     </row>
     <row r="9">
@@ -1621,13 +1621,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1781634400.565237</v>
+        <v>1781635915.82583</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3.182335138320923</v>
+        <v>3.175831079483032</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.04916596412658691</v>
+        <v>0.06370186805725098</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>61</v>
@@ -1657,7 +1657,7 @@
         <v>20003</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>24</v>
@@ -1666,13 +1666,13 @@
         <v>17</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>31336</v>
+        <v>28058</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.04916596412658691</v>
+        <v>0.06370186805725098</v>
       </c>
       <c r="U9" s="2" t="b">
         <v>1</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f2c1810000b7de</t>
+          <t>05640a440200010010f0d2c1810000eac6</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="n">
@@ -1734,19 +1734,19 @@
         </is>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>0.2284866778801916</v>
+        <v>0.2282158931589232</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>0.3323780880539385</v>
+        <v>0.3327429792360728</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>0.1753896246542981</v>
+        <v>0.1754790771845523</v>
       </c>
       <c r="AO9" s="2" t="n">
-        <v>0.141352680343469</v>
+        <v>0.1413187915540336</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>0.1223929290681026</v>
+        <v>0.1222432588664183</v>
       </c>
     </row>
     <row r="10">
@@ -1759,13 +1759,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>1781634401.542224</v>
+        <v>1781635916.811646</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>4.159322023391724</v>
+        <v>4.161647081375122</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.9769868850708008</v>
+        <v>0.9858160018920898</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>68</v>
@@ -1792,7 +1792,7 @@
         <v>128</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O10" s="2" t="n">
         <v>20003</v>
@@ -1804,13 +1804,13 @@
         <v>24</v>
       </c>
       <c r="R10" s="2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S10" s="2" t="n">
-        <v>45809</v>
+        <v>41382</v>
       </c>
       <c r="T10" s="2" t="n">
-        <v>0.9769868850708008</v>
+        <v>0.9858160018920898</v>
       </c>
       <c r="U10" s="2" t="b">
         <v>1</v>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="AI10" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af2c2013c02063c03063c040623a3</t>
+          <t>056411c401000200c35ad2c2013c02063c03063c04061054</t>
         </is>
       </c>
       <c r="AJ10" s="2" t="n">
@@ -1872,19 +1872,19 @@
         </is>
       </c>
       <c r="AL10" s="2" t="n">
-        <v>0.15900195075143</v>
+        <v>0.1589475708900054</v>
       </c>
       <c r="AM10" s="2" t="n">
-        <v>0.2024911482184018</v>
+        <v>0.2025784089207333</v>
       </c>
       <c r="AN10" s="2" t="n">
-        <v>0.2930386274382661</v>
+        <v>0.2933026758542157</v>
       </c>
       <c r="AO10" s="2" t="n">
-        <v>0.2222302578068498</v>
+        <v>0.2220404181840605</v>
       </c>
       <c r="AP10" s="2" t="n">
-        <v>0.1232380157850522</v>
+        <v>0.123130926150985</v>
       </c>
     </row>
     <row r="11">
@@ -1897,13 +1897,13 @@
         <v>10</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>1781634401.812325</v>
+        <v>1781635917.038633</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4.429423093795776</v>
+        <v>4.388634204864502</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>0.2701010704040527</v>
+        <v>0.2269871234893799</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>61</v>
@@ -1933,7 +1933,7 @@
         <v>20003</v>
       </c>
       <c r="O11" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P11" s="2" t="n">
         <v>24</v>
@@ -1942,13 +1942,13 @@
         <v>17</v>
       </c>
       <c r="R11" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S11" s="2" t="n">
-        <v>24581</v>
+        <v>17325</v>
       </c>
       <c r="T11" s="2" t="n">
-        <v>0.2701010704040527</v>
+        <v>0.2269871234893799</v>
       </c>
       <c r="U11" s="2" t="b">
         <v>1</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="AI11" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f3c2810000f0f7</t>
+          <t>05640a440200010010f0d3c2810000adef</t>
         </is>
       </c>
       <c r="AJ11" s="2" t="n">
@@ -2010,19 +2010,19 @@
         </is>
       </c>
       <c r="AL11" s="2" t="n">
-        <v>0.2284872094035421</v>
+        <v>0.2282164103099309</v>
       </c>
       <c r="AM11" s="2" t="n">
-        <v>0.3323777388095467</v>
+        <v>0.3327426418252985</v>
       </c>
       <c r="AN11" s="2" t="n">
-        <v>0.1753894615677761</v>
+        <v>0.1754789205890807</v>
       </c>
       <c r="AO11" s="2" t="n">
-        <v>0.1413527635194767</v>
+        <v>0.1413188661555714</v>
       </c>
       <c r="AP11" s="2" t="n">
-        <v>0.1223928266996585</v>
+        <v>0.1222431611201184</v>
       </c>
     </row>
     <row r="12">
@@ -2035,13 +2035,13 @@
         <v>11</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>1781634402.601039</v>
+        <v>1781635917.861753</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>5.21813702583313</v>
+        <v>5.211754083633423</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.7887139320373535</v>
+        <v>0.8231198787689209</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>68</v>
@@ -2068,7 +2068,7 @@
         <v>128</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O12" s="2" t="n">
         <v>20003</v>
@@ -2080,13 +2080,13 @@
         <v>24</v>
       </c>
       <c r="R12" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S12" s="2" t="n">
-        <v>35602</v>
+        <v>14114</v>
       </c>
       <c r="T12" s="2" t="n">
-        <v>0.7887139320373535</v>
+        <v>0.8231198787689209</v>
       </c>
       <c r="U12" s="2" t="b">
         <v>1</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af3c3013c02063c03063c04064a59</t>
+          <t>056411c401000200c35ad3c3013c02063c03063c040679ae</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="n">
@@ -2148,19 +2148,19 @@
         </is>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>0.1590229378730502</v>
+        <v>0.1589476569539593</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>0.2025181984854179</v>
+        <v>0.2025782844972731</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>0.2929849945732926</v>
+        <v>0.2933024984553666</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>0.22221969595637</v>
+        <v>0.2220406977155613</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>0.1232541731118693</v>
+        <v>0.1231308623778398</v>
       </c>
     </row>
     <row r="13">
@@ -2173,13 +2173,13 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>1781634402.714112</v>
+        <v>1781635917.931688</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>5.331210136413574</v>
+        <v>5.281689167022705</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.1130731105804443</v>
+        <v>0.06993508338928223</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>61</v>
@@ -2209,7 +2209,7 @@
         <v>20003</v>
       </c>
       <c r="O13" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P13" s="2" t="n">
         <v>24</v>
@@ -2218,13 +2218,13 @@
         <v>17</v>
       </c>
       <c r="R13" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S13" s="2" t="n">
-        <v>31425</v>
+        <v>28121</v>
       </c>
       <c r="T13" s="2" t="n">
-        <v>0.1130731105804443</v>
+        <v>0.06993508338928223</v>
       </c>
       <c r="U13" s="2" t="b">
         <v>1</v>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AI13" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f4c38100000adc</t>
+          <t>05640a440200010010f0d4c381000057c4</t>
         </is>
       </c>
       <c r="AJ13" s="2" t="n">
@@ -2286,19 +2286,19 @@
         </is>
       </c>
       <c r="AL13" s="2" t="n">
-        <v>0.2284875949314194</v>
+        <v>0.228216792195782</v>
       </c>
       <c r="AM13" s="2" t="n">
-        <v>0.3323775033245469</v>
+        <v>0.3327424078015567</v>
       </c>
       <c r="AN13" s="2" t="n">
-        <v>0.1753893567517205</v>
+        <v>0.1754788169588296</v>
       </c>
       <c r="AO13" s="2" t="n">
-        <v>0.1413527819360842</v>
+        <v>0.1413188846428216</v>
       </c>
       <c r="AP13" s="2" t="n">
-        <v>0.122392763056229</v>
+        <v>0.1222430984010102</v>
       </c>
     </row>
     <row r="14">
@@ -2311,13 +2311,13 @@
         <v>13</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>1781634403.627071</v>
+        <v>1781635918.881576</v>
       </c>
       <c r="D14" s="2" t="n">
-        <v>6.244168996810913</v>
+        <v>6.231577157974243</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.9129588603973389</v>
+        <v>0.9498879909515381</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>68</v>
@@ -2344,7 +2344,7 @@
         <v>128</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O14" s="2" t="n">
         <v>20003</v>
@@ -2356,13 +2356,13 @@
         <v>24</v>
       </c>
       <c r="R14" s="2" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="S14" s="2" t="n">
-        <v>11549</v>
+        <v>6867</v>
       </c>
       <c r="T14" s="2" t="n">
-        <v>0.9129588603973389</v>
+        <v>0.9498879909515381</v>
       </c>
       <c r="U14" s="2" t="b">
         <v>1</v>
@@ -2412,7 +2412,7 @@
       </c>
       <c r="AI14" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af4c4013c02063c03063c0406a724</t>
+          <t>056411c401000200c35ad4c4013c02063c03063c040694d3</t>
         </is>
       </c>
       <c r="AJ14" s="2" t="n">
@@ -2424,19 +2424,19 @@
         </is>
       </c>
       <c r="AL14" s="2" t="n">
-        <v>0.1590230098236465</v>
+        <v>0.1589477287174308</v>
       </c>
       <c r="AM14" s="2" t="n">
-        <v>0.2025180566661929</v>
+        <v>0.2025781431403125</v>
       </c>
       <c r="AN14" s="2" t="n">
-        <v>0.2929847540645867</v>
+        <v>0.2933022577488878</v>
       </c>
       <c r="AO14" s="2" t="n">
-        <v>0.2222200835848331</v>
+        <v>0.2220410848812981</v>
       </c>
       <c r="AP14" s="2" t="n">
-        <v>0.1232540958607408</v>
+        <v>0.1231307855120707</v>
       </c>
     </row>
     <row r="15">
@@ -2449,13 +2449,13 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>1781634403.648631</v>
+        <v>1781635919.079154</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>6.265729188919067</v>
+        <v>6.429155111312866</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.0215601921081543</v>
+        <v>0.197577953338623</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>61</v>
@@ -2485,7 +2485,7 @@
         <v>20003</v>
       </c>
       <c r="O15" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P15" s="2" t="n">
         <v>24</v>
@@ -2494,13 +2494,13 @@
         <v>17</v>
       </c>
       <c r="R15" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S15" s="2" t="n">
-        <v>11325</v>
+        <v>65484</v>
       </c>
       <c r="T15" s="2" t="n">
-        <v>0.0215601921081543</v>
+        <v>0.197577953338623</v>
       </c>
       <c r="U15" s="2" t="b">
         <v>1</v>
@@ -2550,7 +2550,7 @@
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f5c48100006629</t>
+          <t>05640a440200010010f0d5c48100003b31</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="n">
@@ -2562,19 +2562,19 @@
         </is>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>0.2284953365256042</v>
+        <v>0.2282246235309279</v>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>0.3323908752188612</v>
+        <v>0.3327559914569594</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>0.1753719253113434</v>
+        <v>0.175461205069506</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>0.1413453033985046</v>
+        <v>0.1413113636865075</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>0.1223965595456867</v>
+        <v>0.1222468162560993</v>
       </c>
     </row>
     <row r="16">
@@ -2587,13 +2587,13 @@
         <v>15</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>1781634404.676558</v>
+        <v>1781635919.896824</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>7.29365611076355</v>
+        <v>7.246824979782104</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.027926921844482</v>
+        <v>0.8176698684692383</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>68</v>
@@ -2620,7 +2620,7 @@
         <v>128</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O16" s="2" t="n">
         <v>20003</v>
@@ -2632,13 +2632,13 @@
         <v>24</v>
       </c>
       <c r="R16" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S16" s="2" t="n">
-        <v>1081</v>
+        <v>45395</v>
       </c>
       <c r="T16" s="2" t="n">
-        <v>1.027926921844482</v>
+        <v>0.8176698684692383</v>
       </c>
       <c r="U16" s="2" t="b">
         <v>1</v>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="AI16" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af5c5013c02063c03063c0406cede</t>
+          <t>056411c401000200c35ad5c5013c02063c03063c0406fd29</t>
         </is>
       </c>
       <c r="AJ16" s="2" t="n">
@@ -2700,19 +2700,19 @@
         </is>
       </c>
       <c r="AL16" s="2" t="n">
-        <v>0.1590230841279612</v>
+        <v>0.1589687652935212</v>
       </c>
       <c r="AM16" s="2" t="n">
-        <v>0.2025179125748249</v>
+        <v>0.2026053101431209</v>
       </c>
       <c r="AN16" s="2" t="n">
-        <v>0.2929845104215129</v>
+        <v>0.2932483514186648</v>
       </c>
       <c r="AO16" s="2" t="n">
-        <v>0.2222204751731827</v>
+        <v>0.2220306051807667</v>
       </c>
       <c r="AP16" s="2" t="n">
-        <v>0.1232540177025183</v>
+        <v>0.1231469679639263</v>
       </c>
     </row>
     <row r="17">
@@ -2725,13 +2725,13 @@
         <v>16</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>1781634404.862295</v>
+        <v>1781635920.002884</v>
       </c>
       <c r="D17" s="2" t="n">
-        <v>7.479393005371094</v>
+        <v>7.352885007858276</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.1857368946075439</v>
+        <v>0.1060600280761719</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>61</v>
@@ -2761,7 +2761,7 @@
         <v>20003</v>
       </c>
       <c r="O17" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P17" s="2" t="n">
         <v>24</v>
@@ -2770,13 +2770,13 @@
         <v>17</v>
       </c>
       <c r="R17" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S17" s="2" t="n">
-        <v>50676</v>
+        <v>39172</v>
       </c>
       <c r="T17" s="2" t="n">
-        <v>0.1857368946075439</v>
+        <v>0.1060600280761719</v>
       </c>
       <c r="U17" s="2" t="b">
         <v>1</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AI17" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f6c5810000848e</t>
+          <t>05640a440200010010f0d6c5810000d996</t>
         </is>
       </c>
       <c r="AJ17" s="2" t="n">
@@ -2838,19 +2838,19 @@
         </is>
       </c>
       <c r="AL17" s="2" t="n">
-        <v>0.2284958539734526</v>
+        <v>0.2282250182795221</v>
       </c>
       <c r="AM17" s="2" t="n">
-        <v>0.3323905386439159</v>
+        <v>0.3327557457010931</v>
       </c>
       <c r="AN17" s="2" t="n">
-        <v>0.1753717685529878</v>
+        <v>0.1754610949015154</v>
       </c>
       <c r="AO17" s="2" t="n">
-        <v>0.1413453774279772</v>
+        <v>0.1413113921082294</v>
       </c>
       <c r="AP17" s="2" t="n">
-        <v>0.1223964614016665</v>
+        <v>0.1222467490096399</v>
       </c>
     </row>
     <row r="18">
@@ -2863,13 +2863,13 @@
         <v>17</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>1781634405.694902</v>
+        <v>1781635920.917569</v>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8.312000036239624</v>
+        <v>8.267570018768311</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.8326070308685303</v>
+        <v>0.9146850109100342</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>68</v>
@@ -2896,7 +2896,7 @@
         <v>128</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O18" s="2" t="n">
         <v>20003</v>
@@ -2908,13 +2908,13 @@
         <v>24</v>
       </c>
       <c r="R18" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S18" s="2" t="n">
-        <v>50512</v>
+        <v>28137</v>
       </c>
       <c r="T18" s="2" t="n">
-        <v>0.8326070308685303</v>
+        <v>0.9146850109100342</v>
       </c>
       <c r="U18" s="2" t="b">
         <v>1</v>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af6c6013c02063c03063c04060c9d</t>
+          <t>056411c401000200c35ad6c6013c02063c03063c04063f6a</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="n">
@@ -2976,19 +2976,19 @@
         </is>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>0.1590231687950336</v>
+        <v>0.1589688383715838</v>
       </c>
       <c r="AM18" s="2" t="n">
-        <v>0.2025177947858458</v>
+        <v>0.2026051708095027</v>
       </c>
       <c r="AN18" s="2" t="n">
-        <v>0.2929843479884817</v>
+        <v>0.2932481178467784</v>
       </c>
       <c r="AO18" s="2" t="n">
-        <v>0.2222207306690584</v>
+        <v>0.2220309803948515</v>
       </c>
       <c r="AP18" s="2" t="n">
-        <v>0.1232539577615806</v>
+        <v>0.1231468925772836</v>
       </c>
     </row>
     <row r="19">
@@ -3001,13 +3001,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>1781634405.778453</v>
+        <v>1781635920.983933</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8.395551204681396</v>
+        <v>8.33393406867981</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>0.08355116844177246</v>
+        <v>0.06636404991149902</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>61</v>
@@ -3037,7 +3037,7 @@
         <v>20003</v>
       </c>
       <c r="O19" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P19" s="2" t="n">
         <v>24</v>
@@ -3046,13 +3046,13 @@
         <v>17</v>
       </c>
       <c r="R19" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S19" s="2" t="n">
-        <v>43915</v>
+        <v>28437</v>
       </c>
       <c r="T19" s="2" t="n">
-        <v>0.08355116844177246</v>
+        <v>0.06636404991149902</v>
       </c>
       <c r="U19" s="2" t="b">
         <v>1</v>
@@ -3102,7 +3102,7 @@
       </c>
       <c r="AI19" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f7c6810000c3a7</t>
+          <t>05640a440200010010f0d7c68100009ebf</t>
         </is>
       </c>
       <c r="AJ19" s="2" t="n">
@@ -3114,19 +3114,19 @@
         </is>
       </c>
       <c r="AL19" s="2" t="n">
-        <v>0.2284962454981744</v>
+        <v>0.2282254373211894</v>
       </c>
       <c r="AM19" s="2" t="n">
-        <v>0.3323902958189776</v>
+        <v>0.3327554814932172</v>
       </c>
       <c r="AN19" s="2" t="n">
-        <v>0.1753716598424941</v>
+        <v>0.17546097553484</v>
       </c>
       <c r="AO19" s="2" t="n">
-        <v>0.1413454038267184</v>
+        <v>0.1413114299156355</v>
       </c>
       <c r="AP19" s="2" t="n">
-        <v>0.1223963950136355</v>
+        <v>0.1222466757351178</v>
       </c>
     </row>
     <row r="20">
@@ -3139,13 +3139,13 @@
         <v>19</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>1781634406.730525</v>
+        <v>1781635921.949266</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>9.347623109817505</v>
+        <v>9.299267053604126</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.9520719051361084</v>
+        <v>0.9653329849243164</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>68</v>
@@ -3172,7 +3172,7 @@
         <v>128</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O20" s="2" t="n">
         <v>20003</v>
@@ -3184,13 +3184,13 @@
         <v>24</v>
       </c>
       <c r="R20" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S20" s="2" t="n">
-        <v>27484</v>
+        <v>21913</v>
       </c>
       <c r="T20" s="2" t="n">
-        <v>0.9520719051361084</v>
+        <v>0.9653329849243164</v>
       </c>
       <c r="U20" s="2" t="b">
         <v>1</v>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AI20" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af7c7013c02063c03063c04066567</t>
+          <t>056411c401000200c35ad7c7013c02063c03063c04065690</t>
         </is>
       </c>
       <c r="AJ20" s="2" t="n">
@@ -3252,19 +3252,19 @@
         </is>
       </c>
       <c r="AL20" s="2" t="n">
-        <v>0.1590232417414568</v>
+        <v>0.158968914275862</v>
       </c>
       <c r="AM20" s="2" t="n">
-        <v>0.2025176521035482</v>
+        <v>0.2026050334320464</v>
       </c>
       <c r="AN20" s="2" t="n">
-        <v>0.2929841064510721</v>
+        <v>0.2932478929547491</v>
       </c>
       <c r="AO20" s="2" t="n">
-        <v>0.2222211195215362</v>
+        <v>0.2220313403887952</v>
       </c>
       <c r="AP20" s="2" t="n">
-        <v>0.1232538801823868</v>
+        <v>0.1231468189485473</v>
       </c>
     </row>
     <row r="21">
@@ -3277,13 +3277,13 @@
         <v>20</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>1781634406.768835</v>
+        <v>1781635922.221958</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>9.38593316078186</v>
+        <v>9.571959018707275</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.03831005096435547</v>
+        <v>0.2726919651031494</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>61</v>
@@ -3313,7 +3313,7 @@
         <v>20003</v>
       </c>
       <c r="O21" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P21" s="2" t="n">
         <v>24</v>
@@ -3322,13 +3322,13 @@
         <v>17</v>
       </c>
       <c r="R21" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S21" s="2" t="n">
-        <v>30900</v>
+        <v>27740</v>
       </c>
       <c r="T21" s="2" t="n">
-        <v>0.03831005096435547</v>
+        <v>0.2726919651031494</v>
       </c>
       <c r="U21" s="2" t="b">
         <v>1</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="AI21" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f8c781000070d9</t>
+          <t>05640a440200010010f0d8c78100002dc1</t>
         </is>
       </c>
       <c r="AJ21" s="2" t="n">
@@ -3390,19 +3390,19 @@
         </is>
       </c>
       <c r="AL21" s="2" t="n">
-        <v>0.2284966685085374</v>
+        <v>0.2282259651471433</v>
       </c>
       <c r="AM21" s="2" t="n">
-        <v>0.3323900297571863</v>
+        <v>0.3327551346135788</v>
       </c>
       <c r="AN21" s="2" t="n">
-        <v>0.1753715396393182</v>
+        <v>0.1754608141365076</v>
       </c>
       <c r="AO21" s="2" t="n">
-        <v>0.1413454409697556</v>
+        <v>0.1413115113598827</v>
       </c>
       <c r="AP21" s="2" t="n">
-        <v>0.1223963211252024</v>
+        <v>0.1222465747428874</v>
       </c>
     </row>
     <row r="22">
@@ -3415,13 +3415,13 @@
         <v>21</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>1781634407.782649</v>
+        <v>1781635922.979304</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>10.399747133255</v>
+        <v>10.32930517196655</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1.013813972473145</v>
+        <v>0.7573461532592773</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>68</v>
@@ -3448,7 +3448,7 @@
         <v>128</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O22" s="2" t="n">
         <v>20003</v>
@@ -3460,13 +3460,13 @@
         <v>24</v>
       </c>
       <c r="R22" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S22" s="2" t="n">
-        <v>63794</v>
+        <v>50541</v>
       </c>
       <c r="T22" s="2" t="n">
-        <v>1.013813972473145</v>
+        <v>0.7573461532592773</v>
       </c>
       <c r="U22" s="2" t="b">
         <v>1</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="AI22" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af8c8013c02063c03063c0406d666</t>
+          <t>056411c401000200c35ad8c8013c02063c03063c0406e591</t>
         </is>
       </c>
       <c r="AJ22" s="2" t="n">
@@ -3528,19 +3528,19 @@
         </is>
       </c>
       <c r="AL22" s="2" t="n">
-        <v>0.1590233184168796</v>
+        <v>0.1589690008624353</v>
       </c>
       <c r="AM22" s="2" t="n">
-        <v>0.2025175114862508</v>
+        <v>0.2026049149423349</v>
       </c>
       <c r="AN22" s="2" t="n">
-        <v>0.2929838751122774</v>
+        <v>0.2932477303091908</v>
       </c>
       <c r="AO22" s="2" t="n">
-        <v>0.2222214903929615</v>
+        <v>0.2220315948102478</v>
       </c>
       <c r="AP22" s="2" t="n">
-        <v>0.1232538045916307</v>
+        <v>0.1231467590757914</v>
       </c>
     </row>
     <row r="23">
@@ -3553,13 +3553,13 @@
         <v>22</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>1781634408.031722</v>
+        <v>1781635923.13418</v>
       </c>
       <c r="D23" s="2" t="n">
-        <v>10.64882016181946</v>
+        <v>10.48418116569519</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.2490730285644531</v>
+        <v>0.1548759937286377</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>61</v>
@@ -3589,7 +3589,7 @@
         <v>20003</v>
       </c>
       <c r="O23" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P23" s="2" t="n">
         <v>24</v>
@@ -3598,13 +3598,13 @@
         <v>17</v>
       </c>
       <c r="R23" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S23" s="2" t="n">
-        <v>30663</v>
+        <v>27377</v>
       </c>
       <c r="T23" s="2" t="n">
-        <v>0.2490730285644531</v>
+        <v>0.1548759937286377</v>
       </c>
       <c r="U23" s="2" t="b">
         <v>1</v>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AI23" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0f9c881000033d9</t>
+          <t>05640a440200010010f0d9c88100006ec1</t>
         </is>
       </c>
       <c r="AJ23" s="2" t="n">
@@ -3666,19 +3666,19 @@
         </is>
       </c>
       <c r="AL23" s="2" t="n">
-        <v>0.2284972068409722</v>
+        <v>0.2282263550457767</v>
       </c>
       <c r="AM23" s="2" t="n">
-        <v>0.3323896769698053</v>
+        <v>0.3327548938678557</v>
       </c>
       <c r="AN23" s="2" t="n">
-        <v>0.1753713749840218</v>
+        <v>0.1754607063455053</v>
       </c>
       <c r="AO23" s="2" t="n">
-        <v>0.1413455233882825</v>
+        <v>0.1413115356545541</v>
       </c>
       <c r="AP23" s="2" t="n">
-        <v>0.1223962178169184</v>
+        <v>0.1222465090863082</v>
       </c>
     </row>
     <row r="24">
@@ -3691,13 +3691,13 @@
         <v>23</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>1781634408.829741</v>
+        <v>1781635924.023609</v>
       </c>
       <c r="D24" s="2" t="n">
-        <v>11.44683909416199</v>
+        <v>11.37361001968384</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.7980189323425293</v>
+        <v>0.8894288539886475</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>68</v>
@@ -3724,7 +3724,7 @@
         <v>128</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O24" s="2" t="n">
         <v>20003</v>
@@ -3736,13 +3736,13 @@
         <v>24</v>
       </c>
       <c r="R24" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S24" s="2" t="n">
-        <v>3795</v>
+        <v>7530</v>
       </c>
       <c r="T24" s="2" t="n">
-        <v>0.7980189323425293</v>
+        <v>0.8894288539886475</v>
       </c>
       <c r="U24" s="2" t="b">
         <v>1</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="AI24" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35af9c9013c02063c03063c0406bf9c</t>
+          <t>056411c401000200c35ad9c9013c02063c03063c04068c6b</t>
         </is>
       </c>
       <c r="AJ24" s="2" t="n">
@@ -3804,19 +3804,19 @@
         </is>
       </c>
       <c r="AL24" s="2" t="n">
-        <v>0.159023406166678</v>
+        <v>0.1589690741708274</v>
       </c>
       <c r="AM24" s="2" t="n">
-        <v>0.2025173914823616</v>
+        <v>0.2026047699808858</v>
       </c>
       <c r="AN24" s="2" t="n">
-        <v>0.2929837114899179</v>
+        <v>0.2932474837064077</v>
       </c>
       <c r="AO24" s="2" t="n">
-        <v>0.2222217470414786</v>
+        <v>0.2220319920169252</v>
       </c>
       <c r="AP24" s="2" t="n">
-        <v>0.1232537438195639</v>
+        <v>0.1231466801249539</v>
       </c>
     </row>
     <row r="25">
@@ -3829,13 +3829,13 @@
         <v>24</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>1781634408.962024</v>
+        <v>1781635924.080966</v>
       </c>
       <c r="D25" s="2" t="n">
-        <v>11.5791220664978</v>
+        <v>11.43096709251404</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.1322829723358154</v>
+        <v>0.0573570728302002</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>61</v>
@@ -3865,7 +3865,7 @@
         <v>20003</v>
       </c>
       <c r="O25" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P25" s="2" t="n">
         <v>24</v>
@@ -3874,13 +3874,13 @@
         <v>17</v>
       </c>
       <c r="R25" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S25" s="2" t="n">
-        <v>53503</v>
+        <v>50345</v>
       </c>
       <c r="T25" s="2" t="n">
-        <v>0.1322829723358154</v>
+        <v>0.0573570728302002</v>
       </c>
       <c r="U25" s="2" t="b">
         <v>1</v>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="AI25" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fac9810000d17e</t>
+          <t>05640a440200010010f0dac98100008c66</t>
         </is>
       </c>
       <c r="AJ25" s="2" t="n">
@@ -3942,19 +3942,19 @@
         </is>
       </c>
       <c r="AL25" s="2" t="n">
-        <v>0.2284976044301568</v>
+        <v>0.2282267597010821</v>
       </c>
       <c r="AM25" s="2" t="n">
-        <v>0.3323894315130955</v>
+        <v>0.3327546418385645</v>
       </c>
       <c r="AN25" s="2" t="n">
-        <v>0.1753712650130204</v>
+        <v>0.175460593674957</v>
       </c>
       <c r="AO25" s="2" t="n">
-        <v>0.1413455483446081</v>
+        <v>0.141311564400004</v>
       </c>
       <c r="AP25" s="2" t="n">
-        <v>0.1223961506991192</v>
+        <v>0.1222464403853926</v>
       </c>
     </row>
     <row r="26">
@@ -3967,13 +3967,13 @@
         <v>25</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>1781634409.84501</v>
+        <v>1781635925.043479</v>
       </c>
       <c r="D26" s="2" t="n">
-        <v>12.46210813522339</v>
+        <v>12.39348006248474</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.8829860687255859</v>
+        <v>0.9625129699707031</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>68</v>
@@ -4000,7 +4000,7 @@
         <v>128</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O26" s="2" t="n">
         <v>20003</v>
@@ -4012,13 +4012,13 @@
         <v>24</v>
       </c>
       <c r="R26" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S26" s="2" t="n">
-        <v>20326</v>
+        <v>23171</v>
       </c>
       <c r="T26" s="2" t="n">
-        <v>0.8829860687255859</v>
+        <v>0.9625129699707031</v>
       </c>
       <c r="U26" s="2" t="b">
         <v>1</v>
@@ -4068,7 +4068,7 @@
       </c>
       <c r="AI26" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afaca013c02063c03063c04067ddf</t>
+          <t>056411c401000200c35adaca013c02063c03063c04064e28</t>
         </is>
       </c>
       <c r="AJ26" s="2" t="n">
@@ -4080,19 +4080,19 @@
         </is>
       </c>
       <c r="AL26" s="2" t="n">
-        <v>0.1590234789586656</v>
+        <v>0.1589691482507335</v>
       </c>
       <c r="AM26" s="2" t="n">
-        <v>0.202517253892661</v>
+        <v>0.2026046325184552</v>
       </c>
       <c r="AN26" s="2" t="n">
-        <v>0.2929834825446029</v>
+        <v>0.2932472558599855</v>
       </c>
       <c r="AO26" s="2" t="n">
-        <v>0.2222221152148023</v>
+        <v>0.2220323572370949</v>
       </c>
       <c r="AP26" s="2" t="n">
-        <v>0.1232536693892681</v>
+        <v>0.123146606133731</v>
       </c>
     </row>
     <row r="27">
@@ -4105,13 +4105,13 @@
         <v>26</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>1781634409.883437</v>
+        <v>1781635925.222812</v>
       </c>
       <c r="D27" s="2" t="n">
-        <v>12.5005350112915</v>
+        <v>12.57281303405762</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.03842687606811523</v>
+        <v>0.179332971572876</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>61</v>
@@ -4141,7 +4141,7 @@
         <v>20003</v>
       </c>
       <c r="O27" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P27" s="2" t="n">
         <v>24</v>
@@ -4150,13 +4150,13 @@
         <v>17</v>
       </c>
       <c r="R27" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S27" s="2" t="n">
-        <v>63248</v>
+        <v>55872</v>
       </c>
       <c r="T27" s="2" t="n">
-        <v>0.03842687606811523</v>
+        <v>0.179332971572876</v>
       </c>
       <c r="U27" s="2" t="b">
         <v>1</v>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="AI27" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fbca8100009657</t>
+          <t>05640a440200010010f0dbca810000cb4f</t>
         </is>
       </c>
       <c r="AJ27" s="2" t="n">
@@ -4218,19 +4218,19 @@
         </is>
       </c>
       <c r="AL27" s="2" t="n">
-        <v>0.2284979982048171</v>
+        <v>0.2282272467473996</v>
       </c>
       <c r="AM27" s="2" t="n">
-        <v>0.3323891864976891</v>
+        <v>0.3327543260059256</v>
       </c>
       <c r="AN27" s="2" t="n">
-        <v>0.1753711553966675</v>
+        <v>0.1754604475342879</v>
       </c>
       <c r="AO27" s="2" t="n">
-        <v>0.1413455761671288</v>
+        <v>0.1413116303639429</v>
       </c>
       <c r="AP27" s="2" t="n">
-        <v>0.1223960837336973</v>
+        <v>0.1222463493484441</v>
       </c>
     </row>
     <row r="28">
@@ -4243,13 +4243,13 @@
         <v>27</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>1781634410.862581</v>
+        <v>1781635926.076013</v>
       </c>
       <c r="D28" s="2" t="n">
-        <v>13.47967910766602</v>
+        <v>13.42601418495178</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.9791440963745117</v>
+        <v>0.853201150894165</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>68</v>
@@ -4276,7 +4276,7 @@
         <v>128</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O28" s="2" t="n">
         <v>20003</v>
@@ -4288,13 +4288,13 @@
         <v>24</v>
       </c>
       <c r="R28" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S28" s="2" t="n">
-        <v>47094</v>
+        <v>32687</v>
       </c>
       <c r="T28" s="2" t="n">
-        <v>0.9791440963745117</v>
+        <v>0.853201150894165</v>
       </c>
       <c r="U28" s="2" t="b">
         <v>1</v>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="AI28" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afbcb013c02063c03063c04061425</t>
+          <t>056411c401000200c35adbcb013c02063c03063c040627d2</t>
         </is>
       </c>
       <c r="AJ28" s="2" t="n">
@@ -4356,19 +4356,19 @@
         </is>
       </c>
       <c r="AL28" s="2" t="n">
-        <v>0.1590235515734635</v>
+        <v>0.1589692308097039</v>
       </c>
       <c r="AM28" s="2" t="n">
-        <v>0.202517115252225</v>
+        <v>0.2026045065354884</v>
       </c>
       <c r="AN28" s="2" t="n">
-        <v>0.2929832501445304</v>
+        <v>0.2932470693222604</v>
       </c>
       <c r="AO28" s="2" t="n">
-        <v>0.2222224886918739</v>
+        <v>0.2220326525498661</v>
       </c>
       <c r="AP28" s="2" t="n">
-        <v>0.1232535943379074</v>
+        <v>0.1231465407826811</v>
       </c>
     </row>
     <row r="29">
@@ -4381,13 +4381,13 @@
         <v>28</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>1781634411.141658</v>
+        <v>1781635926.154292</v>
       </c>
       <c r="D29" s="2" t="n">
-        <v>13.75875616073608</v>
+        <v>13.50429320335388</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.2790770530700684</v>
+        <v>0.07827901840209961</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>61</v>
@@ -4417,7 +4417,7 @@
         <v>20003</v>
       </c>
       <c r="O29" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P29" s="2" t="n">
         <v>24</v>
@@ -4426,13 +4426,13 @@
         <v>17</v>
       </c>
       <c r="R29" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S29" s="2" t="n">
-        <v>53520</v>
+        <v>50352</v>
       </c>
       <c r="T29" s="2" t="n">
-        <v>0.2790770530700684</v>
+        <v>0.07827901840209961</v>
       </c>
       <c r="U29" s="2" t="b">
         <v>1</v>
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AI29" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fccb8100006c7c</t>
+          <t>05640a440200010010f0dccb8100003164</t>
         </is>
       </c>
       <c r="AJ29" s="2" t="n">
@@ -4494,19 +4494,19 @@
         </is>
       </c>
       <c r="AL29" s="2" t="n">
-        <v>0.2284985344626978</v>
+        <v>0.2282276448734107</v>
       </c>
       <c r="AM29" s="2" t="n">
-        <v>0.332388833158465</v>
+        <v>0.3327540784584258</v>
       </c>
       <c r="AN29" s="2" t="n">
-        <v>0.1753709901346421</v>
+        <v>0.1754603368582419</v>
       </c>
       <c r="AO29" s="2" t="n">
-        <v>0.1413456623819796</v>
+        <v>0.1413116579266496</v>
       </c>
       <c r="AP29" s="2" t="n">
-        <v>0.1223959798622156</v>
+        <v>0.1222462818832721</v>
       </c>
     </row>
     <row r="30">
@@ -4519,13 +4519,13 @@
         <v>29</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>1781634411.877245</v>
+        <v>1781635927.123585</v>
       </c>
       <c r="D30" s="2" t="n">
-        <v>14.49434304237366</v>
+        <v>14.4735860824585</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.7355868816375732</v>
+        <v>0.9692928791046143</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>68</v>
@@ -4552,7 +4552,7 @@
         <v>128</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O30" s="2" t="n">
         <v>20003</v>
@@ -4564,13 +4564,13 @@
         <v>24</v>
       </c>
       <c r="R30" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S30" s="2" t="n">
-        <v>53656</v>
+        <v>56231</v>
       </c>
       <c r="T30" s="2" t="n">
-        <v>0.7355868816375732</v>
+        <v>0.9692928791046143</v>
       </c>
       <c r="U30" s="2" t="b">
         <v>1</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="AI30" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afccc013c02063c03063c0406f958</t>
+          <t>056411c401000200c35adccc013c02063c03063c0406caaf</t>
         </is>
       </c>
       <c r="AJ30" s="2" t="n">
@@ -4632,19 +4632,19 @@
         </is>
       </c>
       <c r="AL30" s="2" t="n">
-        <v>0.1590236382058882</v>
+        <v>0.1589693051929303</v>
       </c>
       <c r="AM30" s="2" t="n">
-        <v>0.2025170015257222</v>
+        <v>0.2026043623788819</v>
       </c>
       <c r="AN30" s="2" t="n">
-        <v>0.2929830993966349</v>
+        <v>0.2932468254513343</v>
       </c>
       <c r="AO30" s="2" t="n">
-        <v>0.2222227234340954</v>
+        <v>0.222033044353563</v>
       </c>
       <c r="AP30" s="2" t="n">
-        <v>0.1232535374376595</v>
+        <v>0.1231464626232904</v>
       </c>
     </row>
     <row r="31">
@@ -4657,13 +4657,13 @@
         <v>30</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>1781634412.093199</v>
+        <v>1781635927.33484</v>
       </c>
       <c r="D31" s="2" t="n">
-        <v>14.71029710769653</v>
+        <v>14.68484115600586</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>0.215954065322876</v>
+        <v>0.2112550735473633</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>61</v>
@@ -4693,7 +4693,7 @@
         <v>20003</v>
       </c>
       <c r="O31" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P31" s="2" t="n">
         <v>24</v>
@@ -4702,13 +4702,13 @@
         <v>17</v>
       </c>
       <c r="R31" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S31" s="2" t="n">
-        <v>50002</v>
+        <v>38490</v>
       </c>
       <c r="T31" s="2" t="n">
-        <v>0.215954065322876</v>
+        <v>0.2112550735473633</v>
       </c>
       <c r="U31" s="2" t="b">
         <v>1</v>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="AI31" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0fdcc8100000089</t>
+          <t>05640a440200010010f0ddcc8100005d91</t>
         </is>
       </c>
       <c r="AJ31" s="2" t="n">
@@ -4770,19 +4770,19 @@
         </is>
       </c>
       <c r="AL31" s="2" t="n">
-        <v>0.2284989409127082</v>
+        <v>0.2282281484294773</v>
       </c>
       <c r="AM31" s="2" t="n">
-        <v>0.3323885792463092</v>
+        <v>0.3327537513163782</v>
       </c>
       <c r="AN31" s="2" t="n">
-        <v>0.1753708752668529</v>
+        <v>0.1754601855428246</v>
       </c>
       <c r="AO31" s="2" t="n">
-        <v>0.1413456952670647</v>
+        <v>0.1413117271053499</v>
       </c>
       <c r="AP31" s="2" t="n">
-        <v>0.122395909307065</v>
+        <v>0.12224618760597</v>
       </c>
     </row>
     <row r="32">
@@ -4795,19 +4795,19 @@
         <v>31</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>1781634412.376808</v>
+        <v>1781635928.170167</v>
       </c>
       <c r="D32" s="2" t="n">
-        <v>14.99390602111816</v>
+        <v>15.52016806602478</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>0.2836089134216309</v>
+        <v>0.8353269100189209</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
       <c r="I32" s="2" t="inlineStr"/>
@@ -4828,7 +4828,7 @@
         <v>128</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O32" s="2" t="n">
         <v>20003</v>
@@ -4837,16 +4837,16 @@
         <v>24</v>
       </c>
       <c r="Q32" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="R32" s="2" t="n">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="S32" s="2" t="n">
-        <v>45387</v>
+        <v>472</v>
       </c>
       <c r="T32" s="2" t="n">
-        <v>0.2836089134216309</v>
+        <v>0.8353269100189209</v>
       </c>
       <c r="U32" s="2" t="b">
         <v>1</v>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="W32" s="2" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="X32" s="2" t="n">
         <v>196</v>
@@ -4892,11 +4892,11 @@
         </is>
       </c>
       <c r="AH32" s="2" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AI32" s="2" t="inlineStr">
         <is>
-          <t>056414c4010002004aa2fdcd013c01063c02063c03063c04062e4e</t>
+          <t>056411c401000200c35addcd013c02063c03063c0406a355</t>
         </is>
       </c>
       <c r="AJ32" s="2" t="n">
@@ -4908,19 +4908,19 @@
         </is>
       </c>
       <c r="AL32" s="2" t="n">
-        <v>0.1588790190956892</v>
+        <v>0.1589693898446677</v>
       </c>
       <c r="AM32" s="2" t="n">
-        <v>0.2023041887741057</v>
+        <v>0.2026042363542299</v>
       </c>
       <c r="AN32" s="2" t="n">
-        <v>0.2927820480110387</v>
+        <v>0.2932466419155548</v>
       </c>
       <c r="AO32" s="2" t="n">
-        <v>0.2220229140456036</v>
+        <v>0.2220333342794711</v>
       </c>
       <c r="AP32" s="2" t="n">
-        <v>0.1240118300735628</v>
+        <v>0.1231463976060763</v>
       </c>
     </row>
     <row r="33">
@@ -4933,19 +4933,19 @@
         <v>32</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>1781634412.419588</v>
+        <v>1781635928.25484</v>
       </c>
       <c r="D33" s="2" t="n">
-        <v>15.03668618202209</v>
+        <v>15.60484099388123</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>0.04278016090393066</v>
+        <v>0.08467292785644531</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>219</v>
+        <v>61</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>219</v>
+        <v>61</v>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
       <c r="I33" s="2" t="inlineStr"/>
@@ -4969,22 +4969,22 @@
         <v>20003</v>
       </c>
       <c r="O33" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P33" s="2" t="n">
         <v>24</v>
       </c>
       <c r="Q33" s="2" t="n">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="R33" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S33" s="2" t="n">
-        <v>7352</v>
+        <v>61390</v>
       </c>
       <c r="T33" s="2" t="n">
-        <v>0.04278016090393066</v>
+        <v>0.08467292785644531</v>
       </c>
       <c r="U33" s="2" t="b">
         <v>1</v>
@@ -4995,7 +4995,7 @@
         </is>
       </c>
       <c r="W33" s="2" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="X33" s="2" t="n">
         <v>68</v>
@@ -5030,11 +5030,11 @@
         </is>
       </c>
       <c r="AH33" s="2" t="n">
-        <v>175</v>
+        <v>17</v>
       </c>
       <c r="AI33" s="2" t="inlineStr">
         <is>
-          <t>0564964402000100e04efecd810000010200000901010101010165c001010101</t>
+          <t>05640a440200010010f0decd810000bf36</t>
         </is>
       </c>
       <c r="AJ33" s="2" t="n">
@@ -5042,23 +5042,23 @@
       </c>
       <c r="AK33" s="2" t="inlineStr">
         <is>
-          <t>DOS_ATTACK</t>
+          <t>CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AL33" s="2" t="n">
-        <v>0.2035912361455302</v>
+        <v>0.2282285417458954</v>
       </c>
       <c r="AM33" s="2" t="n">
-        <v>0.2411303105565294</v>
+        <v>0.3327535083442836</v>
       </c>
       <c r="AN33" s="2" t="n">
-        <v>0.1694242671237084</v>
+        <v>0.1754600773190438</v>
       </c>
       <c r="AO33" s="2" t="n">
-        <v>0.144125586445444</v>
+        <v>0.141311750766957</v>
       </c>
       <c r="AP33" s="2" t="n">
-        <v>0.241728599728788</v>
+        <v>0.1222461218238202</v>
       </c>
     </row>
     <row r="34">
@@ -5071,13 +5071,13 @@
         <v>33</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>1781634412.89267</v>
+        <v>1781635929.19017</v>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15.50976800918579</v>
+        <v>16.54017114639282</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>0.4730818271636963</v>
+        <v>0.9353301525115967</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>68</v>
@@ -5104,7 +5104,7 @@
         <v>128</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O34" s="2" t="n">
         <v>20003</v>
@@ -5116,13 +5116,13 @@
         <v>24</v>
       </c>
       <c r="R34" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S34" s="2" t="n">
-        <v>29980</v>
+        <v>17133</v>
       </c>
       <c r="T34" s="2" t="n">
-        <v>0.4730818271636963</v>
+        <v>0.9353301525115967</v>
       </c>
       <c r="U34" s="2" t="b">
         <v>1</v>
@@ -5172,7 +5172,7 @@
       </c>
       <c r="AI34" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35afece013c02063c03063c040652e1</t>
+          <t>056411c401000200c35adece013c02063c03063c04066116</t>
         </is>
       </c>
       <c r="AJ34" s="2" t="n">
@@ -5184,19 +5184,19 @@
         </is>
       </c>
       <c r="AL34" s="2" t="n">
-        <v>0.1590446287547354</v>
+        <v>0.1589694627722815</v>
       </c>
       <c r="AM34" s="2" t="n">
-        <v>0.20254405523236</v>
+        <v>0.2026040969110787</v>
       </c>
       <c r="AN34" s="2" t="n">
-        <v>0.2929294959924783</v>
+        <v>0.2932464076916794</v>
       </c>
       <c r="AO34" s="2" t="n">
-        <v>0.2222121111057644</v>
+        <v>0.2220337104807938</v>
       </c>
       <c r="AP34" s="2" t="n">
-        <v>0.1232697089146618</v>
+        <v>0.1231463221441666</v>
       </c>
     </row>
     <row r="35">
@@ -5209,13 +5209,13 @@
         <v>34</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>1781634412.99461</v>
+        <v>1781635929.260946</v>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15.61170816421509</v>
+        <v>16.6109471321106</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>0.1019401550292969</v>
+        <v>0.07077598571777344</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>61</v>
@@ -5245,7 +5245,7 @@
         <v>20003</v>
       </c>
       <c r="O35" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P35" s="2" t="n">
         <v>24</v>
@@ -5254,13 +5254,13 @@
         <v>17</v>
       </c>
       <c r="R35" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S35" s="2" t="n">
-        <v>16825</v>
+        <v>1388</v>
       </c>
       <c r="T35" s="2" t="n">
-        <v>0.1019401550292969</v>
+        <v>0.07077598571777344</v>
       </c>
       <c r="U35" s="2" t="b">
         <v>1</v>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AI35" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0ffce810000a507</t>
+          <t>05640a440200010010f0dfce810000f81f</t>
         </is>
       </c>
       <c r="AJ35" s="2" t="n">
@@ -5322,19 +5322,19 @@
         </is>
       </c>
       <c r="AL35" s="2" t="n">
-        <v>0.2284993261906224</v>
+        <v>0.2282289714015066</v>
       </c>
       <c r="AM35" s="2" t="n">
-        <v>0.3323883411878159</v>
+        <v>0.3327532360680703</v>
       </c>
       <c r="AN35" s="2" t="n">
-        <v>0.1753707688195548</v>
+        <v>0.1754599537446815</v>
       </c>
       <c r="AO35" s="2" t="n">
-        <v>0.1413457194195429</v>
+        <v>0.1413117930335561</v>
       </c>
       <c r="AP35" s="2" t="n">
-        <v>0.1223958443824639</v>
+        <v>0.1222460457521854</v>
       </c>
     </row>
     <row r="36">
@@ -5347,13 +5347,13 @@
         <v>35</v>
       </c>
       <c r="C36" s="2" t="n">
-        <v>1781634413.942496</v>
+        <v>1781635930.196201</v>
       </c>
       <c r="D36" s="2" t="n">
-        <v>16.55959415435791</v>
+        <v>17.54620218276978</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>0.9478859901428223</v>
+        <v>0.9352550506591797</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>68</v>
@@ -5380,7 +5380,7 @@
         <v>128</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O36" s="2" t="n">
         <v>20003</v>
@@ -5392,13 +5392,13 @@
         <v>24</v>
       </c>
       <c r="R36" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S36" s="2" t="n">
-        <v>35768</v>
+        <v>39405</v>
       </c>
       <c r="T36" s="2" t="n">
-        <v>0.9478859901428223</v>
+        <v>0.9352550506591797</v>
       </c>
       <c r="U36" s="2" t="b">
         <v>1</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="AI36" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35affcf013c02063c03063c04063b1b</t>
+          <t>056411c401000200c35adfcf013c02063c03063c040608ec</t>
         </is>
       </c>
       <c r="AJ36" s="2" t="n">
@@ -5460,19 +5460,19 @@
         </is>
       </c>
       <c r="AL36" s="2" t="n">
-        <v>0.1590446867585421</v>
+        <v>0.1589695388140436</v>
       </c>
       <c r="AM36" s="2" t="n">
-        <v>0.2025438845060903</v>
+        <v>0.202603966498836</v>
       </c>
       <c r="AN36" s="2" t="n">
-        <v>0.2929291699441925</v>
+        <v>0.2932462003331422</v>
       </c>
       <c r="AO36" s="2" t="n">
-        <v>0.2222126484606722</v>
+        <v>0.2220340414445429</v>
       </c>
       <c r="AP36" s="2" t="n">
-        <v>0.1232696103305029</v>
+        <v>0.1231462529094352</v>
       </c>
     </row>
     <row r="37">
@@ -5485,13 +5485,13 @@
         <v>36</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>1781634414.010943</v>
+        <v>1781635930.260731</v>
       </c>
       <c r="D37" s="2" t="n">
-        <v>16.62804102897644</v>
+        <v>17.61073207855225</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>0.06844687461853027</v>
+        <v>0.0645298957824707</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>61</v>
@@ -5521,7 +5521,7 @@
         <v>20003</v>
       </c>
       <c r="O37" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P37" s="2" t="n">
         <v>24</v>
@@ -5530,13 +5530,13 @@
         <v>17</v>
       </c>
       <c r="R37" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S37" s="2" t="n">
-        <v>48219</v>
+        <v>20662</v>
       </c>
       <c r="T37" s="2" t="n">
-        <v>0.06844687461853027</v>
+        <v>0.0645298957824707</v>
       </c>
       <c r="U37" s="2" t="b">
         <v>1</v>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="AI37" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c0cf810000d9cb</t>
+          <t>05640a440200010010f0e0cf81000084d3</t>
         </is>
       </c>
       <c r="AJ37" s="2" t="n">
@@ -5598,19 +5598,19 @@
         </is>
       </c>
       <c r="AL37" s="2" t="n">
-        <v>0.2285071063628407</v>
+        <v>0.2282367443318382</v>
       </c>
       <c r="AM37" s="2" t="n">
-        <v>0.3324016162210311</v>
+        <v>0.3327667939832106</v>
       </c>
       <c r="AN37" s="2" t="n">
-        <v>0.1753533502182164</v>
+        <v>0.1754423913918894</v>
       </c>
       <c r="AO37" s="2" t="n">
-        <v>0.1413382744104418</v>
+        <v>0.1413042706399246</v>
       </c>
       <c r="AP37" s="2" t="n">
-        <v>0.1223996527874701</v>
+        <v>0.1222497996531372</v>
       </c>
     </row>
     <row r="38">
@@ -5623,13 +5623,13 @@
         <v>37</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>1781634414.976879</v>
+        <v>1781635931.220135</v>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17.5939769744873</v>
+        <v>18.57013607025146</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>0.9659359455108643</v>
+        <v>0.9594039916992188</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>68</v>
@@ -5656,7 +5656,7 @@
         <v>128</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O38" s="2" t="n">
         <v>20003</v>
@@ -5668,13 +5668,13 @@
         <v>24</v>
       </c>
       <c r="R38" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S38" s="2" t="n">
-        <v>26505</v>
+        <v>62455</v>
       </c>
       <c r="T38" s="2" t="n">
-        <v>0.9659359455108643</v>
+        <v>0.9594039916992188</v>
       </c>
       <c r="U38" s="2" t="b">
         <v>1</v>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AI38" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac0c0013c02063c03063c04069e30</t>
+          <t>056411c401000200c35ae0c0013c02063c03063c0406adc7</t>
         </is>
       </c>
       <c r="AJ38" s="2" t="n">
@@ -5736,19 +5736,19 @@
         </is>
       </c>
       <c r="AL38" s="2" t="n">
-        <v>0.1590447638946003</v>
+        <v>0.1589696152216157</v>
       </c>
       <c r="AM38" s="2" t="n">
-        <v>0.2025437493162008</v>
+        <v>0.2026038320280061</v>
       </c>
       <c r="AN38" s="2" t="n">
-        <v>0.2929289529560804</v>
+        <v>0.2932459834193989</v>
       </c>
       <c r="AO38" s="2" t="n">
-        <v>0.2222129956314182</v>
+        <v>0.2220343881392713</v>
       </c>
       <c r="AP38" s="2" t="n">
-        <v>0.1232695382017003</v>
+        <v>0.123146181191708</v>
       </c>
     </row>
     <row r="39">
@@ -5761,13 +5761,13 @@
         <v>38</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>1781634415.240068</v>
+        <v>1781635931.505275</v>
       </c>
       <c r="D39" s="2" t="n">
-        <v>17.85716605186462</v>
+        <v>18.85527610778809</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>0.2631890773773193</v>
+        <v>0.2851400375366211</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>61</v>
@@ -5797,7 +5797,7 @@
         <v>20003</v>
       </c>
       <c r="O39" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P39" s="2" t="n">
         <v>24</v>
@@ -5806,13 +5806,13 @@
         <v>17</v>
       </c>
       <c r="R39" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S39" s="2" t="n">
-        <v>48000</v>
+        <v>20313</v>
       </c>
       <c r="T39" s="2" t="n">
-        <v>0.2631890773773193</v>
+        <v>0.2851400375366211</v>
       </c>
       <c r="U39" s="2" t="b">
         <v>1</v>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="AI39" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c1c08100009acb</t>
+          <t>05640a440200010010f0e1c0810000c7d3</t>
         </is>
       </c>
       <c r="AJ39" s="2" t="n">
@@ -5874,19 +5874,19 @@
         </is>
       </c>
       <c r="AL39" s="2" t="n">
-        <v>0.2285076304190822</v>
+        <v>0.2282372749532798</v>
       </c>
       <c r="AM39" s="2" t="n">
-        <v>0.3324012730500676</v>
+        <v>0.3327664444288104</v>
       </c>
       <c r="AN39" s="2" t="n">
-        <v>0.1753531905119513</v>
+        <v>0.1754422286423897</v>
       </c>
       <c r="AO39" s="2" t="n">
-        <v>0.141338353333041</v>
+        <v>0.1413043542512826</v>
       </c>
       <c r="AP39" s="2" t="n">
-        <v>0.122399552685858</v>
+        <v>0.1222496977242375</v>
       </c>
     </row>
     <row r="40">
@@ -5899,13 +5899,13 @@
         <v>39</v>
       </c>
       <c r="C40" s="2" t="n">
-        <v>1781634416.025708</v>
+        <v>1781635932.251966</v>
       </c>
       <c r="D40" s="2" t="n">
-        <v>18.64280605316162</v>
+        <v>19.60196709632874</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>0.7856400012969971</v>
+        <v>0.7466909885406494</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>68</v>
@@ -5932,7 +5932,7 @@
         <v>128</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O40" s="2" t="n">
         <v>20003</v>
@@ -5944,13 +5944,13 @@
         <v>24</v>
       </c>
       <c r="R40" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S40" s="2" t="n">
-        <v>3269</v>
+        <v>56407</v>
       </c>
       <c r="T40" s="2" t="n">
-        <v>0.7856400012969971</v>
+        <v>0.7466909885406494</v>
       </c>
       <c r="U40" s="2" t="b">
         <v>1</v>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="AI40" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac1c1013c02063c03063c0406f7ca</t>
+          <t>056411c401000200c35ae1c1013c02063c03063c0406c43d</t>
         </is>
       </c>
       <c r="AJ40" s="2" t="n">
@@ -6012,19 +6012,19 @@
         </is>
       </c>
       <c r="AL40" s="2" t="n">
-        <v>0.1590448504163043</v>
+        <v>0.158969702172835</v>
       </c>
       <c r="AM40" s="2" t="n">
-        <v>0.202543626576288</v>
+        <v>0.2026037136579172</v>
       </c>
       <c r="AN40" s="2" t="n">
-        <v>0.2929287803254892</v>
+        <v>0.293245821446846</v>
       </c>
       <c r="AO40" s="2" t="n">
-        <v>0.2222132671372586</v>
+        <v>0.2220346412458589</v>
       </c>
       <c r="AP40" s="2" t="n">
-        <v>0.12326947554466</v>
+        <v>0.1231461214765428</v>
       </c>
     </row>
     <row r="41">
@@ -6037,13 +6037,13 @@
         <v>40</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>1781634416.075425</v>
+        <v>1781635932.407184</v>
       </c>
       <c r="D41" s="2" t="n">
-        <v>18.69252300262451</v>
+        <v>19.7571849822998</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>0.04971694946289062</v>
+        <v>0.1552178859710693</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>61</v>
@@ -6073,7 +6073,7 @@
         <v>20003</v>
       </c>
       <c r="O41" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P41" s="2" t="n">
         <v>24</v>
@@ -6082,13 +6082,13 @@
         <v>17</v>
       </c>
       <c r="R41" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S41" s="2" t="n">
-        <v>6521</v>
+        <v>44497</v>
       </c>
       <c r="T41" s="2" t="n">
-        <v>0.04971694946289062</v>
+        <v>0.1552178859710693</v>
       </c>
       <c r="U41" s="2" t="b">
         <v>1</v>
@@ -6138,7 +6138,7 @@
       </c>
       <c r="AI41" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c2c1810000786c</t>
+          <t>05640a440200010010f0e2c18100002574</t>
         </is>
       </c>
       <c r="AJ41" s="2" t="n">
@@ -6150,19 +6150,19 @@
         </is>
       </c>
       <c r="AL41" s="2" t="n">
-        <v>0.2285079878984128</v>
+        <v>0.228237660525537</v>
       </c>
       <c r="AM41" s="2" t="n">
-        <v>0.3324010580596245</v>
+        <v>0.3327662071858919</v>
       </c>
       <c r="AN41" s="2" t="n">
-        <v>0.1753530963837751</v>
+        <v>0.1754421226141869</v>
       </c>
       <c r="AO41" s="2" t="n">
-        <v>0.1413383615560687</v>
+        <v>0.141304376452374</v>
       </c>
       <c r="AP41" s="2" t="n">
-        <v>0.1223994961021188</v>
+        <v>0.12224963322201</v>
       </c>
     </row>
     <row r="42">
@@ -6175,13 +6175,13 @@
         <v>41</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>1781634417.05745</v>
+        <v>1781635933.264632</v>
       </c>
       <c r="D42" s="2" t="n">
-        <v>19.67454814910889</v>
+        <v>20.61463308334351</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>0.982025146484375</v>
+        <v>0.8574481010437012</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>68</v>
@@ -6208,7 +6208,7 @@
         <v>128</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O42" s="2" t="n">
         <v>20003</v>
@@ -6220,13 +6220,13 @@
         <v>24</v>
       </c>
       <c r="R42" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S42" s="2" t="n">
-        <v>52700</v>
+        <v>39149</v>
       </c>
       <c r="T42" s="2" t="n">
-        <v>0.982025146484375</v>
+        <v>0.8574481010437012</v>
       </c>
       <c r="U42" s="2" t="b">
         <v>1</v>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="AI42" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac2c2013c02063c03063c04063589</t>
+          <t>056411c401000200c35ae2c2013c02063c03063c0406067e</t>
         </is>
       </c>
       <c r="AJ42" s="2" t="n">
@@ -6288,19 +6288,19 @@
         </is>
       </c>
       <c r="AL42" s="2" t="n">
-        <v>0.1590449198769318</v>
+        <v>0.158969773967378</v>
       </c>
       <c r="AM42" s="2" t="n">
-        <v>0.2025434788439687</v>
+        <v>0.2026035743262291</v>
       </c>
       <c r="AN42" s="2" t="n">
-        <v>0.2929285213656685</v>
+        <v>0.2932455864947764</v>
       </c>
       <c r="AO42" s="2" t="n">
-        <v>0.2222136857438489</v>
+        <v>0.222035019400479</v>
       </c>
       <c r="AP42" s="2" t="n">
-        <v>0.1232693941695822</v>
+        <v>0.1231460458111376</v>
       </c>
     </row>
     <row r="43">
@@ -6313,13 +6313,13 @@
         <v>42</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>1781634417.337114</v>
+        <v>1781635933.326019</v>
       </c>
       <c r="D43" s="2" t="n">
-        <v>19.9542121887207</v>
+        <v>20.67602014541626</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>0.2796640396118164</v>
+        <v>0.06138706207275391</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>61</v>
@@ -6349,7 +6349,7 @@
         <v>20003</v>
       </c>
       <c r="O43" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P43" s="2" t="n">
         <v>24</v>
@@ -6358,13 +6358,13 @@
         <v>17</v>
       </c>
       <c r="R43" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S43" s="2" t="n">
-        <v>16264</v>
+        <v>50026</v>
       </c>
       <c r="T43" s="2" t="n">
-        <v>0.2796640396118164</v>
+        <v>0.06138706207275391</v>
       </c>
       <c r="U43" s="2" t="b">
         <v>1</v>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="AI43" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c3c28100003f45</t>
+          <t>05640a440200010010f0e3c2810000625d</t>
         </is>
       </c>
       <c r="AJ43" s="2" t="n">
@@ -6426,19 +6426,19 @@
         </is>
       </c>
       <c r="AL43" s="2" t="n">
-        <v>0.2285085257323099</v>
+        <v>0.2282380532715022</v>
       </c>
       <c r="AM43" s="2" t="n">
-        <v>0.3324007042073942</v>
+        <v>0.3327659625292319</v>
       </c>
       <c r="AN43" s="2" t="n">
-        <v>0.175352931192523</v>
+        <v>0.1754420132452645</v>
       </c>
       <c r="AO43" s="2" t="n">
-        <v>0.1413384465149454</v>
+        <v>0.1413044044351453</v>
       </c>
       <c r="AP43" s="2" t="n">
-        <v>0.1223993923528275</v>
+        <v>0.1222495665188559</v>
       </c>
     </row>
     <row r="44">
@@ -6451,13 +6451,13 @@
         <v>43</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>1781634418.07669</v>
+        <v>1781635934.305225</v>
       </c>
       <c r="D44" s="2" t="n">
-        <v>20.69378805160522</v>
+        <v>21.65522599220276</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>0.7395758628845215</v>
+        <v>0.979205846786499</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>68</v>
@@ -6484,7 +6484,7 @@
         <v>128</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O44" s="2" t="n">
         <v>20003</v>
@@ -6496,13 +6496,13 @@
         <v>24</v>
       </c>
       <c r="R44" s="2" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S44" s="2" t="n">
-        <v>42440</v>
+        <v>11965</v>
       </c>
       <c r="T44" s="2" t="n">
-        <v>0.7395758628845215</v>
+        <v>0.979205846786499</v>
       </c>
       <c r="U44" s="2" t="b">
         <v>1</v>
@@ -6552,7 +6552,7 @@
       </c>
       <c r="AI44" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac3c3013c02063c03063c04065c73</t>
+          <t>056411c401000200c35ae3c3013c02063c03063c04066f84</t>
         </is>
       </c>
       <c r="AJ44" s="2" t="n">
@@ -6564,19 +6564,19 @@
         </is>
       </c>
       <c r="AL44" s="2" t="n">
-        <v>0.159045006830657</v>
+        <v>0.1589698476045383</v>
       </c>
       <c r="AM44" s="2" t="n">
-        <v>0.2025433644488539</v>
+        <v>0.202603430669918</v>
       </c>
       <c r="AN44" s="2" t="n">
-        <v>0.2929283694920423</v>
+        <v>0.2932453426495865</v>
       </c>
       <c r="AO44" s="2" t="n">
-        <v>0.2222139223355865</v>
+        <v>0.2220354112246006</v>
       </c>
       <c r="AP44" s="2" t="n">
-        <v>0.1232693368928603</v>
+        <v>0.1231459678513566</v>
       </c>
     </row>
     <row r="45">
@@ -6589,13 +6589,13 @@
         <v>44</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>1781634418.226298</v>
+        <v>1781635934.368615</v>
       </c>
       <c r="D45" s="2" t="n">
-        <v>20.84339618682861</v>
+        <v>21.71861600875854</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>0.1496081352233887</v>
+        <v>0.06339001655578613</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>61</v>
@@ -6625,7 +6625,7 @@
         <v>20003</v>
       </c>
       <c r="O45" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P45" s="2" t="n">
         <v>24</v>
@@ -6634,13 +6634,13 @@
         <v>17</v>
       </c>
       <c r="R45" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S45" s="2" t="n">
-        <v>5336</v>
+        <v>43274</v>
       </c>
       <c r="T45" s="2" t="n">
-        <v>0.1496081352233887</v>
+        <v>0.06339001655578613</v>
       </c>
       <c r="U45" s="2" t="b">
         <v>1</v>
@@ -6690,7 +6690,7 @@
       </c>
       <c r="AI45" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c4c3810000c56e</t>
+          <t>05640a440200010010f0e4c38100009876</t>
         </is>
       </c>
       <c r="AJ45" s="2" t="n">
@@ -6702,19 +6702,19 @@
         </is>
       </c>
       <c r="AL45" s="2" t="n">
-        <v>0.22850890583533</v>
+        <v>0.2282384984737206</v>
       </c>
       <c r="AM45" s="2" t="n">
-        <v>0.3324004707923125</v>
+        <v>0.3327656795771514</v>
       </c>
       <c r="AN45" s="2" t="n">
-        <v>0.1753528267891284</v>
+        <v>0.1754418844919607</v>
       </c>
       <c r="AO45" s="2" t="n">
-        <v>0.1413384678511497</v>
+        <v>0.1413044503417473</v>
       </c>
       <c r="AP45" s="2" t="n">
-        <v>0.1223993287320795</v>
+        <v>0.1222494871154199</v>
       </c>
     </row>
     <row r="46">
@@ -6727,13 +6727,13 @@
         <v>45</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>1781634419.1076</v>
+        <v>1781635935.34917</v>
       </c>
       <c r="D46" s="2" t="n">
-        <v>21.72469806671143</v>
+        <v>22.69917106628418</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>0.8813018798828125</v>
+        <v>0.9805550575256348</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>68</v>
@@ -6760,7 +6760,7 @@
         <v>128</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O46" s="2" t="n">
         <v>20003</v>
@@ -6772,13 +6772,13 @@
         <v>24</v>
       </c>
       <c r="R46" s="2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S46" s="2" t="n">
-        <v>20483</v>
+        <v>6687</v>
       </c>
       <c r="T46" s="2" t="n">
-        <v>0.8813018798828125</v>
+        <v>0.9805550575256348</v>
       </c>
       <c r="U46" s="2" t="b">
         <v>1</v>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="AI46" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac4c4013c02063c03063c0406b10e</t>
+          <t>056411c401000200c35ae4c4013c02063c03063c040682f9</t>
         </is>
       </c>
       <c r="AJ46" s="2" t="n">
@@ -6840,19 +6840,19 @@
         </is>
       </c>
       <c r="AL46" s="2" t="n">
-        <v>0.1590450783674019</v>
+        <v>0.1589908835072025</v>
       </c>
       <c r="AM46" s="2" t="n">
-        <v>0.2025432206995551</v>
+        <v>0.2026305762825527</v>
       </c>
       <c r="AN46" s="2" t="n">
-        <v>0.2929281241300312</v>
+        <v>0.293191404574112</v>
       </c>
       <c r="AO46" s="2" t="n">
-        <v>0.2222143185051579</v>
+        <v>0.2220249881647358</v>
       </c>
       <c r="AP46" s="2" t="n">
-        <v>0.1232692582978539</v>
+        <v>0.123162147471397</v>
       </c>
     </row>
     <row r="47">
@@ -6865,13 +6865,13 @@
         <v>46</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>1781634419.135407</v>
+        <v>1781635935.618579</v>
       </c>
       <c r="D47" s="2" t="n">
-        <v>21.75250506401062</v>
+        <v>22.9685800075531</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>0.02780699729919434</v>
+        <v>0.2694089412689209</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>61</v>
@@ -6901,7 +6901,7 @@
         <v>20003</v>
       </c>
       <c r="O47" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P47" s="2" t="n">
         <v>24</v>
@@ -6910,13 +6910,13 @@
         <v>17</v>
       </c>
       <c r="R47" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S47" s="2" t="n">
-        <v>59081</v>
+        <v>39556</v>
       </c>
       <c r="T47" s="2" t="n">
-        <v>0.02780699729919434</v>
+        <v>0.2694089412689209</v>
       </c>
       <c r="U47" s="2" t="b">
         <v>1</v>
@@ -6966,7 +6966,7 @@
       </c>
       <c r="AI47" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c5c4810000a99b</t>
+          <t>05640a440200010010f0e5c4810000f483</t>
         </is>
       </c>
       <c r="AJ47" s="2" t="n">
@@ -6978,19 +6978,19 @@
         </is>
       </c>
       <c r="AL47" s="2" t="n">
-        <v>0.2285092945134609</v>
+        <v>0.2282390314676469</v>
       </c>
       <c r="AM47" s="2" t="n">
-        <v>0.3324002304216784</v>
+        <v>0.3327653294446415</v>
       </c>
       <c r="AN47" s="2" t="n">
-        <v>0.1753527199034792</v>
+        <v>0.1754417216446578</v>
       </c>
       <c r="AO47" s="2" t="n">
-        <v>0.1413384914928953</v>
+        <v>0.1413045322275925</v>
       </c>
       <c r="AP47" s="2" t="n">
-        <v>0.1223992636684862</v>
+        <v>0.1222493852154614</v>
       </c>
     </row>
     <row r="48">
@@ -7003,13 +7003,13 @@
         <v>47</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>1781634420.13423</v>
+        <v>1781635936.36531</v>
       </c>
       <c r="D48" s="2" t="n">
-        <v>22.7513279914856</v>
+        <v>23.71531105041504</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>0.9988229274749756</v>
+        <v>0.7467310428619385</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>68</v>
@@ -7036,7 +7036,7 @@
         <v>128</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O48" s="2" t="n">
         <v>20003</v>
@@ -7048,13 +7048,13 @@
         <v>24</v>
       </c>
       <c r="R48" s="2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S48" s="2" t="n">
-        <v>9971</v>
+        <v>45290</v>
       </c>
       <c r="T48" s="2" t="n">
-        <v>0.9988229274749756</v>
+        <v>0.7467310428619385</v>
       </c>
       <c r="U48" s="2" t="b">
         <v>1</v>
@@ -7104,7 +7104,7 @@
       </c>
       <c r="AI48" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac5c5013c02063c03063c0406d8f4</t>
+          <t>056411c401000200c35ae5c5013c02063c03063c0406eb03</t>
         </is>
       </c>
       <c r="AJ48" s="2" t="n">
@@ -7116,19 +7116,19 @@
         </is>
       </c>
       <c r="AL48" s="2" t="n">
-        <v>0.1590451508370368</v>
+        <v>0.158990970160732</v>
       </c>
       <c r="AM48" s="2" t="n">
-        <v>0.2025430793659663</v>
+        <v>0.2026304614672162</v>
       </c>
       <c r="AN48" s="2" t="n">
-        <v>0.2929278847885661</v>
+        <v>0.2931912510168236</v>
       </c>
       <c r="AO48" s="2" t="n">
-        <v>0.2222147034701472</v>
+        <v>0.2220252274267783</v>
       </c>
       <c r="AP48" s="2" t="n">
-        <v>0.1232691815382836</v>
+        <v>0.1231620899284499</v>
       </c>
     </row>
     <row r="49">
@@ -7141,13 +7141,13 @@
         <v>48</v>
       </c>
       <c r="C49" s="2" t="n">
-        <v>1781634420.371863</v>
+        <v>1781635936.552831</v>
       </c>
       <c r="D49" s="2" t="n">
-        <v>22.98896098136902</v>
+        <v>23.90283203125</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>0.2376329898834229</v>
+        <v>0.1875209808349609</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>61</v>
@@ -7177,7 +7177,7 @@
         <v>20003</v>
       </c>
       <c r="O49" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P49" s="2" t="n">
         <v>24</v>
@@ -7186,13 +7186,13 @@
         <v>17</v>
       </c>
       <c r="R49" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S49" s="2" t="n">
-        <v>17662</v>
+        <v>63800</v>
       </c>
       <c r="T49" s="2" t="n">
-        <v>0.2376329898834229</v>
+        <v>0.1875209808349609</v>
       </c>
       <c r="U49" s="2" t="b">
         <v>1</v>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="AI49" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c6c58100004b3c</t>
+          <t>05640a440200010010f0e6c58100001624</t>
         </is>
       </c>
       <c r="AJ49" s="2" t="n">
@@ -7254,19 +7254,19 @@
         </is>
       </c>
       <c r="AL49" s="2" t="n">
-        <v>0.2285098216192725</v>
+        <v>0.2282394306944385</v>
       </c>
       <c r="AM49" s="2" t="n">
-        <v>0.332399884931911</v>
+        <v>0.3327650807092409</v>
       </c>
       <c r="AN49" s="2" t="n">
-        <v>0.1753525585261108</v>
+        <v>0.1754416096611968</v>
       </c>
       <c r="AO49" s="2" t="n">
-        <v>0.1413385725631103</v>
+        <v>0.1413045622220699</v>
       </c>
       <c r="AP49" s="2" t="n">
-        <v>0.1223991623595955</v>
+        <v>0.1222493167130536</v>
       </c>
     </row>
     <row r="50">
@@ -7279,13 +7279,13 @@
         <v>49</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>1781634421.167259</v>
+        <v>1781635937.397351</v>
       </c>
       <c r="D50" s="2" t="n">
-        <v>23.78435707092285</v>
+        <v>24.7473521232605</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>0.795396089553833</v>
+        <v>0.844520092010498</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>68</v>
@@ -7312,7 +7312,7 @@
         <v>128</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O50" s="2" t="n">
         <v>20003</v>
@@ -7324,13 +7324,13 @@
         <v>24</v>
       </c>
       <c r="R50" s="2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S50" s="2" t="n">
-        <v>58374</v>
+        <v>29060</v>
       </c>
       <c r="T50" s="2" t="n">
-        <v>0.795396089553833</v>
+        <v>0.844520092010498</v>
       </c>
       <c r="U50" s="2" t="b">
         <v>1</v>
@@ -7380,7 +7380,7 @@
       </c>
       <c r="AI50" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac6c6013c02063c03063c04061ab7</t>
+          <t>056411c401000200c35ae6c6013c02063c03063c04062940</t>
         </is>
       </c>
       <c r="AJ50" s="2" t="n">
@@ -7392,19 +7392,19 @@
         </is>
       </c>
       <c r="AL50" s="2" t="n">
-        <v>0.1590452370804389</v>
+        <v>0.1589910440019669</v>
       </c>
       <c r="AM50" s="2" t="n">
-        <v>0.2025429603122807</v>
+        <v>0.202630320572157</v>
       </c>
       <c r="AN50" s="2" t="n">
-        <v>0.2929277210696155</v>
+        <v>0.293191015271374</v>
       </c>
       <c r="AO50" s="2" t="n">
-        <v>0.222214960411295</v>
+        <v>0.2220256065263544</v>
       </c>
       <c r="AP50" s="2" t="n">
-        <v>0.1232691211263699</v>
+        <v>0.1231620136281479</v>
       </c>
     </row>
     <row r="51">
@@ -7417,13 +7417,13 @@
         <v>50</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>1781634421.305892</v>
+        <v>1781635937.469843</v>
       </c>
       <c r="D51" s="2" t="n">
-        <v>23.92299008369446</v>
+        <v>24.81984400749207</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>0.1386330127716064</v>
+        <v>0.07249188423156738</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>61</v>
@@ -7453,7 +7453,7 @@
         <v>20003</v>
       </c>
       <c r="O51" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P51" s="2" t="n">
         <v>24</v>
@@ -7462,13 +7462,13 @@
         <v>17</v>
       </c>
       <c r="R51" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S51" s="2" t="n">
-        <v>27411</v>
+        <v>3796</v>
       </c>
       <c r="T51" s="2" t="n">
-        <v>0.1386330127716064</v>
+        <v>0.07249188423156738</v>
       </c>
       <c r="U51" s="2" t="b">
         <v>1</v>
@@ -7518,7 +7518,7 @@
       </c>
       <c r="AI51" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c7c68100000c15</t>
+          <t>05640a440200010010f0e7c6810000510d</t>
         </is>
       </c>
       <c r="AJ51" s="2" t="n">
@@ -7530,19 +7530,19 @@
         </is>
       </c>
       <c r="AL51" s="2" t="n">
-        <v>0.2285102207870341</v>
+        <v>0.2282398227445749</v>
       </c>
       <c r="AM51" s="2" t="n">
-        <v>0.3323996374169137</v>
+        <v>0.3327648377552994</v>
       </c>
       <c r="AN51" s="2" t="n">
-        <v>0.1753524473843933</v>
+        <v>0.1754415013759076</v>
       </c>
       <c r="AO51" s="2" t="n">
-        <v>0.1413386000223584</v>
+        <v>0.1413045873037266</v>
       </c>
       <c r="AP51" s="2" t="n">
-        <v>0.1223990943893005</v>
+        <v>0.1222492508204915</v>
       </c>
     </row>
     <row r="52">
@@ -7555,13 +7555,13 @@
         <v>51</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>1781634422.216948</v>
+        <v>1781635938.418714</v>
       </c>
       <c r="D52" s="2" t="n">
-        <v>24.83404612541199</v>
+        <v>25.76871514320374</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>0.9110560417175293</v>
+        <v>0.9488711357116699</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>68</v>
@@ -7588,7 +7588,7 @@
         <v>128</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O52" s="2" t="n">
         <v>20003</v>
@@ -7600,13 +7600,13 @@
         <v>24</v>
       </c>
       <c r="R52" s="2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="S52" s="2" t="n">
-        <v>35398</v>
+        <v>22752</v>
       </c>
       <c r="T52" s="2" t="n">
-        <v>0.9110560417175293</v>
+        <v>0.9488711357116699</v>
       </c>
       <c r="U52" s="2" t="b">
         <v>1</v>
@@ -7656,7 +7656,7 @@
       </c>
       <c r="AI52" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac7c7013c02063c03063c0406734d</t>
+          <t>056411c401000200c35ae7c7013c02063c03063c040640ba</t>
         </is>
       </c>
       <c r="AJ52" s="2" t="n">
@@ -7668,19 +7668,19 @@
         </is>
       </c>
       <c r="AL52" s="2" t="n">
-        <v>0.159045311220275</v>
+        <v>0.1589911169053394</v>
       </c>
       <c r="AM52" s="2" t="n">
-        <v>0.2025428160590885</v>
+        <v>0.2026301806548211</v>
       </c>
       <c r="AN52" s="2" t="n">
-        <v>0.2929274778049509</v>
+        <v>0.2931907797785043</v>
       </c>
       <c r="AO52" s="2" t="n">
-        <v>0.2222153521946409</v>
+        <v>0.2220259847887229</v>
       </c>
       <c r="AP52" s="2" t="n">
-        <v>0.1232690427210449</v>
+        <v>0.1231619378726123</v>
       </c>
     </row>
     <row r="53">
@@ -7693,13 +7693,13 @@
         <v>52</v>
       </c>
       <c r="C53" s="2" t="n">
-        <v>1781634422.260353</v>
+        <v>1781635938.693197</v>
       </c>
       <c r="D53" s="2" t="n">
-        <v>24.87745118141174</v>
+        <v>26.0431981086731</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>0.04340505599975586</v>
+        <v>0.2744829654693604</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>61</v>
@@ -7729,7 +7729,7 @@
         <v>20003</v>
       </c>
       <c r="O53" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P53" s="2" t="n">
         <v>24</v>
@@ -7738,13 +7738,13 @@
         <v>17</v>
       </c>
       <c r="R53" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S53" s="2" t="n">
-        <v>4918</v>
+        <v>42776</v>
       </c>
       <c r="T53" s="2" t="n">
-        <v>0.04340505599975586</v>
+        <v>0.2744829654693604</v>
       </c>
       <c r="U53" s="2" t="b">
         <v>1</v>
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AI53" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c8c7810000bf6b</t>
+          <t>05640a440200010010f0e8c7810000e273</t>
         </is>
       </c>
       <c r="AJ53" s="2" t="n">
@@ -7806,19 +7806,19 @@
         </is>
       </c>
       <c r="AL53" s="2" t="n">
-        <v>0.2285106287244395</v>
+        <v>0.2282403444107164</v>
       </c>
       <c r="AM53" s="2" t="n">
-        <v>0.3323993835020165</v>
+        <v>0.3327644949399655</v>
       </c>
       <c r="AN53" s="2" t="n">
-        <v>0.1753523337545319</v>
+        <v>0.1754413420099354</v>
       </c>
       <c r="AO53" s="2" t="n">
-        <v>0.1413386290751684</v>
+        <v>0.1413046675282203</v>
       </c>
       <c r="AP53" s="2" t="n">
-        <v>0.1223990249438438</v>
+        <v>0.1222491511111626</v>
       </c>
     </row>
     <row r="54">
@@ -7831,13 +7831,13 @@
         <v>53</v>
       </c>
       <c r="C54" s="2" t="n">
-        <v>1781634423.261593</v>
+        <v>1781635939.459365</v>
       </c>
       <c r="D54" s="2" t="n">
-        <v>25.87869119644165</v>
+        <v>26.80936598777771</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>1.001240015029907</v>
+        <v>0.7661678791046143</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>68</v>
@@ -7864,7 +7864,7 @@
         <v>128</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O54" s="2" t="n">
         <v>20003</v>
@@ -7876,13 +7876,13 @@
         <v>24</v>
       </c>
       <c r="R54" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S54" s="2" t="n">
-        <v>15390</v>
+        <v>42164</v>
       </c>
       <c r="T54" s="2" t="n">
-        <v>1.001240015029907</v>
+        <v>0.7661678791046143</v>
       </c>
       <c r="U54" s="2" t="b">
         <v>1</v>
@@ -7932,7 +7932,7 @@
       </c>
       <c r="AI54" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac8c8013c02063c03063c0406c04c</t>
+          <t>056411c401000200c35ae8c8013c02063c03063c0406f3bb</t>
         </is>
       </c>
       <c r="AJ54" s="2" t="n">
@@ -7944,19 +7944,19 @@
         </is>
       </c>
       <c r="AL54" s="2" t="n">
-        <v>0.159066290793104</v>
+        <v>0.1589912032842321</v>
       </c>
       <c r="AM54" s="2" t="n">
-        <v>0.202569832012785</v>
+        <v>0.2026300589735328</v>
       </c>
       <c r="AN54" s="2" t="n">
-        <v>0.2928737924385801</v>
+        <v>0.2931906089192193</v>
       </c>
       <c r="AO54" s="2" t="n">
-        <v>0.2222048861121008</v>
+        <v>0.2220262528686021</v>
       </c>
       <c r="AP54" s="2" t="n">
-        <v>0.1232851986434302</v>
+        <v>0.1231618759544138</v>
       </c>
     </row>
     <row r="55">
@@ -7969,13 +7969,13 @@
         <v>54</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1781634423.538738</v>
+        <v>1781635939.59686</v>
       </c>
       <c r="D55" s="2" t="n">
-        <v>26.15583610534668</v>
+        <v>26.94686102867126</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>0.2771449089050293</v>
+        <v>0.1374950408935547</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>61</v>
@@ -8005,7 +8005,7 @@
         <v>20003</v>
       </c>
       <c r="O55" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P55" s="2" t="n">
         <v>24</v>
@@ -8014,13 +8014,13 @@
         <v>17</v>
       </c>
       <c r="R55" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S55" s="2" t="n">
-        <v>4559</v>
+        <v>42543</v>
       </c>
       <c r="T55" s="2" t="n">
-        <v>0.2771449089050293</v>
+        <v>0.1374950408935547</v>
       </c>
       <c r="U55" s="2" t="b">
         <v>1</v>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AI55" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0c9c8810000fc6b</t>
+          <t>05640a440200010010f0e9c8810000a173</t>
         </is>
       </c>
       <c r="AJ55" s="2" t="n">
@@ -8082,19 +8082,19 @@
         </is>
       </c>
       <c r="AL55" s="2" t="n">
-        <v>0.2285111736895782</v>
+        <v>0.2282407307876327</v>
       </c>
       <c r="AM55" s="2" t="n">
-        <v>0.3323990249694449</v>
+        <v>0.3327642574611243</v>
       </c>
       <c r="AN55" s="2" t="n">
-        <v>0.1753521663259802</v>
+        <v>0.1754412360924406</v>
       </c>
       <c r="AO55" s="2" t="n">
-        <v>0.141338715238073</v>
+        <v>0.1413046889133862</v>
       </c>
       <c r="AP55" s="2" t="n">
-        <v>0.1223989197769238</v>
+        <v>0.1222490867454162</v>
       </c>
     </row>
     <row r="56">
@@ -8107,13 +8107,13 @@
         <v>55</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1781634424.309561</v>
+        <v>1781635940.472832</v>
       </c>
       <c r="D56" s="2" t="n">
-        <v>26.92665910720825</v>
+        <v>27.82283306121826</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>0.7708230018615723</v>
+        <v>0.8759720325469971</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>68</v>
@@ -8140,7 +8140,7 @@
         <v>128</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O56" s="2" t="n">
         <v>20003</v>
@@ -8152,13 +8152,13 @@
         <v>24</v>
       </c>
       <c r="R56" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S56" s="2" t="n">
-        <v>20874</v>
+        <v>64772</v>
       </c>
       <c r="T56" s="2" t="n">
-        <v>0.7708230018615723</v>
+        <v>0.8759720325469971</v>
       </c>
       <c r="U56" s="2" t="b">
         <v>1</v>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="AI56" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35ac9c9013c02063c03063c0406a9b6</t>
+          <t>056411c401000200c35ae9c9013c02063c03063c04069a41</t>
         </is>
       </c>
       <c r="AJ56" s="2" t="n">
@@ -8220,19 +8220,19 @@
         </is>
       </c>
       <c r="AL56" s="2" t="n">
-        <v>0.1590663793562386</v>
+        <v>0.1589912752461509</v>
       </c>
       <c r="AM56" s="2" t="n">
-        <v>0.2025697129991564</v>
+        <v>0.2026299196298838</v>
       </c>
       <c r="AN56" s="2" t="n">
-        <v>0.2928736320665936</v>
+        <v>0.2931903740516348</v>
       </c>
       <c r="AO56" s="2" t="n">
-        <v>0.2222051369071745</v>
+        <v>0.2220266307448401</v>
       </c>
       <c r="AP56" s="2" t="n">
-        <v>0.123285138670837</v>
+        <v>0.1231618003274903</v>
       </c>
     </row>
     <row r="57">
@@ -8245,13 +8245,13 @@
         <v>56</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>1781634424.502405</v>
+        <v>1781635940.540956</v>
       </c>
       <c r="D57" s="2" t="n">
-        <v>27.11950302124023</v>
+        <v>27.89095711708069</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>0.1928439140319824</v>
+        <v>0.06812405586242676</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>61</v>
@@ -8281,7 +8281,7 @@
         <v>20003</v>
       </c>
       <c r="O57" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P57" s="2" t="n">
         <v>24</v>
@@ -8290,13 +8290,13 @@
         <v>17</v>
       </c>
       <c r="R57" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S57" s="2" t="n">
-        <v>45186</v>
+        <v>17507</v>
       </c>
       <c r="T57" s="2" t="n">
-        <v>0.1928439140319824</v>
+        <v>0.06812405586242676</v>
       </c>
       <c r="U57" s="2" t="b">
         <v>1</v>
@@ -8346,7 +8346,7 @@
       </c>
       <c r="AI57" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cac98100001ecc</t>
+          <t>05640a440200010010f0eac981000043d4</t>
         </is>
       </c>
       <c r="AJ57" s="2" t="n">
@@ -8358,19 +8358,19 @@
         </is>
       </c>
       <c r="AL57" s="2" t="n">
-        <v>0.2285115854437758</v>
+        <v>0.2282411342423991</v>
       </c>
       <c r="AM57" s="2" t="n">
-        <v>0.3323987688922566</v>
+        <v>0.3327640046918882</v>
       </c>
       <c r="AN57" s="2" t="n">
-        <v>0.175352050844567</v>
+        <v>0.1754411225657156</v>
       </c>
       <c r="AO57" s="2" t="n">
-        <v>0.1413387458352124</v>
+        <v>0.1413047212064439</v>
       </c>
       <c r="AP57" s="2" t="n">
-        <v>0.1223988489841884</v>
+        <v>0.1222490172935533</v>
       </c>
     </row>
     <row r="58">
@@ -8383,13 +8383,13 @@
         <v>57</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>1781634425.353295</v>
+        <v>1781635941.515885</v>
       </c>
       <c r="D58" s="2" t="n">
-        <v>27.97039318084717</v>
+        <v>28.86588621139526</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>0.8508901596069336</v>
+        <v>0.9749290943145752</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>68</v>
@@ -8416,7 +8416,7 @@
         <v>128</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="O58" s="2" t="n">
         <v>20003</v>
@@ -8428,13 +8428,13 @@
         <v>24</v>
       </c>
       <c r="R58" s="2" t="n">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="S58" s="2" t="n">
-        <v>36385</v>
+        <v>15898</v>
       </c>
       <c r="T58" s="2" t="n">
-        <v>0.8508901596069336</v>
+        <v>0.9749290943145752</v>
       </c>
       <c r="U58" s="2" t="b">
         <v>1</v>
@@ -8484,7 +8484,7 @@
       </c>
       <c r="AI58" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35acaca013c02063c03063c04066bf5</t>
+          <t>056411c401000200c35aeaca013c02063c03063c04065802</t>
         </is>
       </c>
       <c r="AJ58" s="2" t="n">
@@ -8496,19 +8496,19 @@
         </is>
       </c>
       <c r="AL58" s="2" t="n">
-        <v>0.1590664545390022</v>
+        <v>0.1589913500556567</v>
       </c>
       <c r="AM58" s="2" t="n">
-        <v>0.2025695720813923</v>
+        <v>0.2026297773078497</v>
       </c>
       <c r="AN58" s="2" t="n">
-        <v>0.2928733987154573</v>
+        <v>0.2931901352698015</v>
       </c>
       <c r="AO58" s="2" t="n">
-        <v>0.2222055121374459</v>
+        <v>0.2220270139594233</v>
       </c>
       <c r="AP58" s="2" t="n">
-        <v>0.1232850625267022</v>
+        <v>0.1231617234072687</v>
       </c>
     </row>
     <row r="59">
@@ -8521,13 +8521,13 @@
         <v>58</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>1781634425.457543</v>
+        <v>1781635941.789272</v>
       </c>
       <c r="D59" s="2" t="n">
-        <v>28.07464098930359</v>
+        <v>29.13927316665649</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>0.1042478084564209</v>
+        <v>0.2733869552612305</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>61</v>
@@ -8557,7 +8557,7 @@
         <v>20003</v>
       </c>
       <c r="O59" s="2" t="n">
-        <v>63396</v>
+        <v>63207</v>
       </c>
       <c r="P59" s="2" t="n">
         <v>24</v>
@@ -8566,13 +8566,13 @@
         <v>17</v>
       </c>
       <c r="R59" s="2" t="n">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="S59" s="2" t="n">
-        <v>38430</v>
+        <v>6777</v>
       </c>
       <c r="T59" s="2" t="n">
-        <v>0.1042478084564209</v>
+        <v>0.2733869552612305</v>
       </c>
       <c r="U59" s="2" t="b">
         <v>1</v>
@@ -8622,7 +8622,7 @@
       </c>
       <c r="AI59" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0cbca81000059e5</t>
+          <t>05640a440200010010f0ebca81000004fd</t>
         </is>
       </c>
       <c r="AJ59" s="2" t="n">
@@ -8634,295 +8634,19 @@
         </is>
       </c>
       <c r="AL59" s="2" t="n">
-        <v>0.2285193436150429</v>
+        <v>0.228249016633985</v>
       </c>
       <c r="AM59" s="2" t="n">
-        <v>0.3324119914089995</v>
+        <v>0.3327774112306197</v>
       </c>
       <c r="AN59" s="2" t="n">
-        <v>0.1753346675580142</v>
+        <v>0.1754235463694086</v>
       </c>
       <c r="AO59" s="2" t="n">
-        <v>0.1413313133672851</v>
+        <v>0.1412972601523176</v>
       </c>
       <c r="AP59" s="2" t="n">
-        <v>0.1224026840506584</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>live_capture</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>59</v>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>1781634426.379002</v>
-      </c>
-      <c r="D60" s="2" t="n">
-        <v>28.99610018730164</v>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>0.9214591979980469</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="G60" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="2" t="inlineStr"/>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M60" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N60" s="2" t="n">
-        <v>63396</v>
-      </c>
-      <c r="O60" s="2" t="n">
-        <v>20003</v>
-      </c>
-      <c r="P60" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q60" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="R60" s="2" t="n">
-        <v>249</v>
-      </c>
-      <c r="S60" s="2" t="n">
-        <v>63197</v>
-      </c>
-      <c r="T60" s="2" t="n">
-        <v>0.9214591979980469</v>
-      </c>
-      <c r="U60" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>0x0564</t>
-        </is>
-      </c>
-      <c r="W60" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="X60" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="Y60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="Z60" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG60" s="2" t="inlineStr">
-        <is>
-          <t>READ</t>
-        </is>
-      </c>
-      <c r="AH60" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI60" s="2" t="inlineStr">
-        <is>
-          <t>056411c401000200c35acbcb013c02063c03063c0406020f</t>
-        </is>
-      </c>
-      <c r="AJ60" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK60" s="2" t="inlineStr">
-        <is>
-          <t>DNP3_RECON</t>
-        </is>
-      </c>
-      <c r="AL60" s="2" t="n">
-        <v>0.1590665288471727</v>
-      </c>
-      <c r="AM60" s="2" t="n">
-        <v>0.202569434222754</v>
-      </c>
-      <c r="AN60" s="2" t="n">
-        <v>0.2928731711079362</v>
-      </c>
-      <c r="AO60" s="2" t="n">
-        <v>0.2222058776045307</v>
-      </c>
-      <c r="AP60" s="2" t="n">
-        <v>0.1232849882176065</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>live_capture</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>1781634426.424383</v>
-      </c>
-      <c r="D61" s="2" t="n">
-        <v>29.04148101806641</v>
-      </c>
-      <c r="E61" s="2" t="n">
-        <v>0.04538083076477051</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="G61" s="2" t="n">
-        <v>61</v>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>127.0.0.1</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="M61" s="2" t="n">
-        <v>128</v>
-      </c>
-      <c r="N61" s="2" t="n">
-        <v>20003</v>
-      </c>
-      <c r="O61" s="2" t="n">
-        <v>63396</v>
-      </c>
-      <c r="P61" s="2" t="n">
-        <v>24</v>
-      </c>
-      <c r="Q61" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="R61" s="2" t="n">
-        <v>248</v>
-      </c>
-      <c r="S61" s="2" t="n">
-        <v>43946</v>
-      </c>
-      <c r="T61" s="2" t="n">
-        <v>0.04538083076477051</v>
-      </c>
-      <c r="U61" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>0x0564</t>
-        </is>
-      </c>
-      <c r="W61" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="X61" s="2" t="n">
-        <v>68</v>
-      </c>
-      <c r="Y61" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB61" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD61" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF61" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="AG61" s="2" t="inlineStr">
-        <is>
-          <t>RESPONSE</t>
-        </is>
-      </c>
-      <c r="AH61" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI61" s="2" t="inlineStr">
-        <is>
-          <t>05640a440200010010f0cccb810000a3ce</t>
-        </is>
-      </c>
-      <c r="AJ61" s="2" t="n">
-        <v>129</v>
-      </c>
-      <c r="AK61" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL_ATTACK</t>
-        </is>
-      </c>
-      <c r="AL61" s="2" t="n">
-        <v>0.2285197567191219</v>
-      </c>
-      <c r="AM61" s="2" t="n">
-        <v>0.3324117323096279</v>
-      </c>
-      <c r="AN61" s="2" t="n">
-        <v>0.1753345508693253</v>
-      </c>
-      <c r="AO61" s="2" t="n">
-        <v>0.141331347678033</v>
-      </c>
-      <c r="AP61" s="2" t="n">
-        <v>0.122402612423892</v>
+        <v>0.1222527656136691</v>
       </c>
     </row>
   </sheetData>

--- a/DNP3/dnp3_capture_with_predictions.xlsx
+++ b/DNP3/dnp3_capture_with_predictions.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP9"/>
+  <dimension ref="A1:AP59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -623,27 +623,27 @@
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>prob_RESTART_ATTACK</t>
+          <t>score_RESTART_ATTACK</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>prob_CONTROL_ATTACK</t>
+          <t>score_CONTROL_ATTACK</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>prob_DNP3_RECON</t>
+          <t>score_DNP3_RECON</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>prob_REPLAY_ATTACK</t>
+          <t>score_REPLAY_ATTACK</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>prob_DOS_ATTACK</t>
+          <t>score_DOS_ATTACK</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>1781776281.040352</v>
+        <v>1781982836.082422</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>128</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="O2" s="2" t="n">
         <v>20003</v>
@@ -700,10 +700,10 @@
         <v>24</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>38772</v>
+        <v>50686</v>
       </c>
       <c r="T2" s="2" t="n">
         <v>0</v>
@@ -756,7 +756,7 @@
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35adccc013c02063c03063c0406caaf</t>
+          <t>056411c401000200c35ac8c8013c02063c03063c0406c04c</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="n">
@@ -764,23 +764,23 @@
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>REPLAY_ATTACK</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>0.63</v>
+        <v>0.2065079739448024</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09356913847729244</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.26</v>
+        <v>0.2245905206838614</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>0.05</v>
+        <v>0.2888083875110841</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>0.03</v>
+        <v>0.1865239793829598</v>
       </c>
     </row>
     <row r="3">
@@ -793,13 +793,13 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>1781776281.237572</v>
+        <v>1781982836.305981</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.1972198486328125</v>
+        <v>0.2235589027404785</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.1972198486328125</v>
+        <v>0.2235589027404785</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>61</v>
@@ -829,7 +829,7 @@
         <v>20003</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="P3" s="2" t="n">
         <v>24</v>
@@ -838,13 +838,13 @@
         <v>17</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S3" s="2" t="n">
-        <v>21031</v>
+        <v>39854</v>
       </c>
       <c r="T3" s="2" t="n">
-        <v>0.1972198486328125</v>
+        <v>0.2235589027404785</v>
       </c>
       <c r="U3" s="2" t="b">
         <v>1</v>
@@ -894,7 +894,7 @@
       </c>
       <c r="AI3" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0ddcc8100005d91</t>
+          <t>05640a440200010010f0c9c8810000fc6b</t>
         </is>
       </c>
       <c r="AJ3" s="2" t="n">
@@ -902,23 +902,23 @@
       </c>
       <c r="AK3" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DNP3_RECON</t>
         </is>
       </c>
       <c r="AL3" s="2" t="n">
-        <v>0.68</v>
+        <v>0.1630104310488283</v>
       </c>
       <c r="AM3" s="2" t="n">
-        <v>0.04</v>
+        <v>0.08859445139363531</v>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.02</v>
+        <v>0.3218242795045348</v>
       </c>
       <c r="AO3" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1995755822193752</v>
       </c>
       <c r="AP3" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2269952558336264</v>
       </c>
     </row>
     <row r="4">
@@ -931,13 +931,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>1781776282.065632</v>
+        <v>1781982837.115806</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1.025279998779297</v>
+        <v>1.033384084701538</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.8280601501464844</v>
+        <v>0.8098251819610596</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>68</v>
@@ -964,7 +964,7 @@
         <v>128</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="O4" s="2" t="n">
         <v>20003</v>
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="R4" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S4" s="2" t="n">
-        <v>48548</v>
+        <v>56170</v>
       </c>
       <c r="T4" s="2" t="n">
-        <v>0.8280601501464844</v>
+        <v>0.8098251819610596</v>
       </c>
       <c r="U4" s="2" t="b">
         <v>1</v>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AI4" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35addcd013c02063c03063c0406a355</t>
+          <t>056411c401000200c35ac9c9013c02063c03063c0406a9b6</t>
         </is>
       </c>
       <c r="AJ4" s="2" t="n">
@@ -1040,23 +1040,23 @@
       </c>
       <c r="AK4" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>REPLAY_ATTACK</t>
         </is>
       </c>
       <c r="AL4" s="2" t="n">
-        <v>0.62</v>
+        <v>0.2066077923822458</v>
       </c>
       <c r="AM4" s="2" t="n">
-        <v>0.04</v>
+        <v>0.09375660031489724</v>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.24</v>
+        <v>0.2242918493607727</v>
       </c>
       <c r="AO4" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2889682279207245</v>
       </c>
       <c r="AP4" s="2" t="n">
-        <v>0.03</v>
+        <v>0.1863755300213597</v>
       </c>
     </row>
     <row r="5">
@@ -1069,13 +1069,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>1781776282.107452</v>
+        <v>1781982837.191616</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1.067099809646606</v>
+        <v>1.109194040298462</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.04181981086730957</v>
+        <v>0.07580995559692383</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>61</v>
@@ -1105,7 +1105,7 @@
         <v>20003</v>
       </c>
       <c r="O5" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="P5" s="2" t="n">
         <v>24</v>
@@ -1114,13 +1114,13 @@
         <v>17</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="S5" s="2" t="n">
-        <v>43931</v>
+        <v>14946</v>
       </c>
       <c r="T5" s="2" t="n">
-        <v>0.04181981086730957</v>
+        <v>0.07580995559692383</v>
       </c>
       <c r="U5" s="2" t="b">
         <v>1</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="AI5" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0decd810000bf36</t>
+          <t>05640a440200010010f0cac98100001ecc</t>
         </is>
       </c>
       <c r="AJ5" s="2" t="n">
@@ -1178,23 +1178,23 @@
       </c>
       <c r="AK5" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DNP3_RECON</t>
         </is>
       </c>
       <c r="AL5" s="2" t="n">
-        <v>0.67</v>
+        <v>0.1629871068494547</v>
       </c>
       <c r="AM5" s="2" t="n">
-        <v>0.05</v>
+        <v>0.08856257990596245</v>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.02</v>
+        <v>0.3218950529092233</v>
       </c>
       <c r="AO5" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1995315962073348</v>
       </c>
       <c r="AP5" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2270236641280249</v>
       </c>
     </row>
     <row r="6">
@@ -1207,13 +1207,13 @@
         <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>1781776283.072625</v>
+        <v>1781982838.149536</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>2.032272815704346</v>
+        <v>2.067113876342773</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0.9651730060577393</v>
+        <v>0.9579198360443115</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>68</v>
@@ -1240,7 +1240,7 @@
         <v>128</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="O6" s="2" t="n">
         <v>20003</v>
@@ -1252,13 +1252,13 @@
         <v>24</v>
       </c>
       <c r="R6" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S6" s="2" t="n">
-        <v>65209</v>
+        <v>6146</v>
       </c>
       <c r="T6" s="2" t="n">
-        <v>0.9651730060577393</v>
+        <v>0.9579198360443115</v>
       </c>
       <c r="U6" s="2" t="b">
         <v>1</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="AI6" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35adece013c02063c03063c04066116</t>
+          <t>056411c401000200c35acaca013c02063c03063c04066bf5</t>
         </is>
       </c>
       <c r="AJ6" s="2" t="n">
@@ -1316,23 +1316,23 @@
       </c>
       <c r="AK6" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>REPLAY_ATTACK</t>
         </is>
       </c>
       <c r="AL6" s="2" t="n">
-        <v>0.62</v>
+        <v>0.2066425334561793</v>
       </c>
       <c r="AM6" s="2" t="n">
-        <v>0.04</v>
+        <v>0.09382056976732106</v>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.24</v>
+        <v>0.2242377847563545</v>
       </c>
       <c r="AO6" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2889252035877654</v>
       </c>
       <c r="AP6" s="2" t="n">
-        <v>0.03</v>
+        <v>0.1863739084323798</v>
       </c>
     </row>
     <row r="7">
@@ -1345,13 +1345,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>1781776283.27112</v>
+        <v>1781982838.432545</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2.230767965316772</v>
+        <v>2.350122928619385</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>0.1984951496124268</v>
+        <v>0.2830090522766113</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>61</v>
@@ -1381,7 +1381,7 @@
         <v>20003</v>
       </c>
       <c r="O7" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="P7" s="2" t="n">
         <v>24</v>
@@ -1390,13 +1390,13 @@
         <v>17</v>
       </c>
       <c r="R7" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S7" s="2" t="n">
-        <v>49464</v>
+        <v>8190</v>
       </c>
       <c r="T7" s="2" t="n">
-        <v>0.1984951496124268</v>
+        <v>0.2830090522766113</v>
       </c>
       <c r="U7" s="2" t="b">
         <v>1</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0dfce810000f81f</t>
+          <t>05640a440200010010f0cbca81000059e5</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="n">
@@ -1454,23 +1454,23 @@
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DNP3_RECON</t>
         </is>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>0.68</v>
+        <v>0.1630050539648707</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>0.04</v>
+        <v>0.08860991336959363</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>0.02</v>
+        <v>0.3218104651005014</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1995634815977419</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2270110859672924</v>
       </c>
     </row>
     <row r="8">
@@ -1483,13 +1483,13 @@
         <v>7</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>1781776284.111945</v>
+        <v>1781982839.169958</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>3.071592807769775</v>
+        <v>3.087536096572876</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.8408248424530029</v>
+        <v>0.7374131679534912</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>68</v>
@@ -1516,7 +1516,7 @@
         <v>128</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="O8" s="2" t="n">
         <v>20003</v>
@@ -1528,13 +1528,13 @@
         <v>24</v>
       </c>
       <c r="R8" s="2" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="S8" s="2" t="n">
-        <v>21946</v>
+        <v>32958</v>
       </c>
       <c r="T8" s="2" t="n">
-        <v>0.8408248424530029</v>
+        <v>0.7374131679534912</v>
       </c>
       <c r="U8" s="2" t="b">
         <v>1</v>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AI8" s="2" t="inlineStr">
         <is>
-          <t>056411c401000200c35adfcf013c02063c03063c040608ec</t>
+          <t>056411c401000200c35acbcb013c02063c03063c0406020f</t>
         </is>
       </c>
       <c r="AJ8" s="2" t="n">
@@ -1592,23 +1592,23 @@
       </c>
       <c r="AK8" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>REPLAY_ATTACK</t>
         </is>
       </c>
       <c r="AL8" s="2" t="n">
-        <v>0.62</v>
+        <v>0.2065996044422008</v>
       </c>
       <c r="AM8" s="2" t="n">
-        <v>0.04</v>
+        <v>0.09372425043276722</v>
       </c>
       <c r="AN8" s="2" t="n">
-        <v>0.24</v>
+        <v>0.2243133882594163</v>
       </c>
       <c r="AO8" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2889800160767814</v>
       </c>
       <c r="AP8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.1863827407888345</v>
       </c>
     </row>
     <row r="9">
@@ -1621,13 +1621,13 @@
         <v>8</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>1781776284.14492</v>
+        <v>1781982839.338631</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3.104568004608154</v>
+        <v>3.256208896636963</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.03297519683837891</v>
+        <v>0.1686728000640869</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>61</v>
@@ -1657,7 +1657,7 @@
         <v>20003</v>
       </c>
       <c r="O9" s="2" t="n">
-        <v>63260</v>
+        <v>65130</v>
       </c>
       <c r="P9" s="2" t="n">
         <v>24</v>
@@ -1666,13 +1666,13 @@
         <v>17</v>
       </c>
       <c r="R9" s="2" t="n">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="S9" s="2" t="n">
-        <v>3203</v>
+        <v>13706</v>
       </c>
       <c r="T9" s="2" t="n">
-        <v>0.03297519683837891</v>
+        <v>0.1686728000640869</v>
       </c>
       <c r="U9" s="2" t="b">
         <v>1</v>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AI9" s="2" t="inlineStr">
         <is>
-          <t>05640a440200010010f0e0cf81000084d3</t>
+          <t>05640a440200010010f0cccb810000a3ce</t>
         </is>
       </c>
       <c r="AJ9" s="2" t="n">
@@ -1730,23 +1730,6923 @@
       </c>
       <c r="AK9" s="2" t="inlineStr">
         <is>
-          <t>RESTART_ATTACK</t>
+          <t>DNP3_RECON</t>
         </is>
       </c>
       <c r="AL9" s="2" t="n">
-        <v>0.67</v>
+        <v>0.1629815049228326</v>
       </c>
       <c r="AM9" s="2" t="n">
-        <v>0.05</v>
+        <v>0.08858011086186571</v>
       </c>
       <c r="AN9" s="2" t="n">
-        <v>0.02</v>
+        <v>0.3218808783347893</v>
       </c>
       <c r="AO9" s="2" t="n">
-        <v>0.08</v>
+        <v>0.1995248543861804</v>
       </c>
       <c r="AP9" s="2" t="n">
-        <v>0.18</v>
+        <v>0.2270326514943319</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>1781982840.186478</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>4.104055881500244</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.8478469848632812</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R10" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S10" s="2" t="n">
+        <v>37424</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0.8478469848632812</v>
+      </c>
+      <c r="U10" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35acccc013c02063c03063c0406ef72</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>0.2066242270064076</v>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>0.09376709058418983</v>
+      </c>
+      <c r="AN10" s="2" t="n">
+        <v>0.2242722347447827</v>
+      </c>
+      <c r="AO10" s="2" t="n">
+        <v>0.2889580054024091</v>
+      </c>
+      <c r="AP10" s="2" t="n">
+        <v>0.1863784422622107</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>1781982840.242293</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>4.159870862960815</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.05581498146057129</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q11" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R11" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S11" s="2" t="n">
+        <v>50996</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0.05581498146057129</v>
+      </c>
+      <c r="U11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG11" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH11" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0cdcc810000cf3b</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK11" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL11" s="2" t="n">
+        <v>0.1629661247128321</v>
+      </c>
+      <c r="AM11" s="2" t="n">
+        <v>0.08855751645070618</v>
+      </c>
+      <c r="AN11" s="2" t="n">
+        <v>0.3219278506617281</v>
+      </c>
+      <c r="AO11" s="2" t="n">
+        <v>0.1994922727072618</v>
+      </c>
+      <c r="AP11" s="2" t="n">
+        <v>0.2270562354674719</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>1781982841.216666</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5.134243965148926</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.9743731021881104</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R12" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S12" s="2" t="n">
+        <v>63984</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0.9743731021881104</v>
+      </c>
+      <c r="U12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X12" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH12" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35acdcd013c02063c03063c04068688</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK12" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL12" s="2" t="n">
+        <v>0.2066550009398102</v>
+      </c>
+      <c r="AM12" s="2" t="n">
+        <v>0.09382299703947786</v>
+      </c>
+      <c r="AN12" s="2" t="n">
+        <v>0.2242258674218055</v>
+      </c>
+      <c r="AO12" s="2" t="n">
+        <v>0.2889176929021844</v>
+      </c>
+      <c r="AP12" s="2" t="n">
+        <v>0.1863784416967221</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>1781982841.254582</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>5.172159910202026</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.03791594505310059</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q13" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R13" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S13" s="2" t="n">
+        <v>26028</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>0.03791594505310059</v>
+      </c>
+      <c r="U13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH13" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0cecd8100002d9c</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>0.1629638024456629</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>0.08855263959995589</v>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>0.3219345646314096</v>
+      </c>
+      <c r="AO13" s="2" t="n">
+        <v>0.1994844435447476</v>
+      </c>
+      <c r="AP13" s="2" t="n">
+        <v>0.227064549778224</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>1781982842.254794</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>6.172371864318848</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1.000211954116821</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R14" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S14" s="2" t="n">
+        <v>14980</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>1.000211954116821</v>
+      </c>
+      <c r="U14" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH14" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35acece013c02063c03063c040644cb</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>0.2066640094201685</v>
+      </c>
+      <c r="AM14" s="2" t="n">
+        <v>0.09383379944360315</v>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>0.2242147960011764</v>
+      </c>
+      <c r="AO14" s="2" t="n">
+        <v>0.2889070907377757</v>
+      </c>
+      <c r="AP14" s="2" t="n">
+        <v>0.1863803043972764</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>1781982842.303592</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>6.221169948577881</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.0487980842590332</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P15" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R15" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S15" s="2" t="n">
+        <v>19269</v>
+      </c>
+      <c r="T15" s="2" t="n">
+        <v>0.0487980842590332</v>
+      </c>
+      <c r="U15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF15" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG15" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH15" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0cfce8100006ab5</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK15" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL15" s="2" t="n">
+        <v>0.1629640377158246</v>
+      </c>
+      <c r="AM15" s="2" t="n">
+        <v>0.08855191017563412</v>
+      </c>
+      <c r="AN15" s="2" t="n">
+        <v>0.3219330862416268</v>
+      </c>
+      <c r="AO15" s="2" t="n">
+        <v>0.1994831099103058</v>
+      </c>
+      <c r="AP15" s="2" t="n">
+        <v>0.2270678559566088</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>1781982843.27093</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>7.188508033752441</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.9673380851745605</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R16" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>20724</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>0.9673380851745605</v>
+      </c>
+      <c r="U16" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH16" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35acfcf013c02063c03063c04062d31</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="n">
+        <v>0.2066591776168013</v>
+      </c>
+      <c r="AM16" s="2" t="n">
+        <v>0.0938159335802532</v>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>0.224224169109176</v>
+      </c>
+      <c r="AO16" s="2" t="n">
+        <v>0.2889193777172854</v>
+      </c>
+      <c r="AP16" s="2" t="n">
+        <v>0.1863813419764841</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>1781982843.337655</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>7.2552330493927</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.06672501564025879</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P17" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q17" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R17" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S17" s="2" t="n">
+        <v>40506</v>
+      </c>
+      <c r="T17" s="2" t="n">
+        <v>0.06672501564025879</v>
+      </c>
+      <c r="U17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF17" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG17" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH17" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d0cf8100004b61</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK17" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL17" s="2" t="n">
+        <v>0.1629650656057162</v>
+      </c>
+      <c r="AM17" s="2" t="n">
+        <v>0.08855237858300799</v>
+      </c>
+      <c r="AN17" s="2" t="n">
+        <v>0.3219291368230108</v>
+      </c>
+      <c r="AO17" s="2" t="n">
+        <v>0.1994835599113032</v>
+      </c>
+      <c r="AP17" s="2" t="n">
+        <v>0.2270698590769618</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>1781982844.318909</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>8.236486911773682</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.9812538623809814</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H18" s="2" t="inlineStr"/>
+      <c r="I18" s="2" t="inlineStr"/>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O18" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R18" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S18" s="2" t="n">
+        <v>49437</v>
+      </c>
+      <c r="T18" s="2" t="n">
+        <v>0.9812538623809814</v>
+      </c>
+      <c r="U18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI18" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad0c0013c02063c03063c0406bbed</t>
+        </is>
+      </c>
+      <c r="AJ18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK18" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL18" s="2" t="n">
+        <v>0.2066653772572522</v>
+      </c>
+      <c r="AM18" s="2" t="n">
+        <v>0.09382079979857161</v>
+      </c>
+      <c r="AN18" s="2" t="n">
+        <v>0.2242172133214318</v>
+      </c>
+      <c r="AO18" s="2" t="n">
+        <v>0.2889136207974519</v>
+      </c>
+      <c r="AP18" s="2" t="n">
+        <v>0.1863829888252925</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>1781982844.596574</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>8.514152050018311</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.2776651382446289</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H19" s="2" t="inlineStr"/>
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P19" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R19" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S19" s="2" t="n">
+        <v>40291</v>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>0.2776651382446289</v>
+      </c>
+      <c r="U19" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d1c08100000861</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="n">
+        <v>0.1629995565187856</v>
+      </c>
+      <c r="AM19" s="2" t="n">
+        <v>0.08859485554097621</v>
+      </c>
+      <c r="AN19" s="2" t="n">
+        <v>0.3218235650569782</v>
+      </c>
+      <c r="AO19" s="2" t="n">
+        <v>0.1995392174921175</v>
+      </c>
+      <c r="AP19" s="2" t="n">
+        <v>0.2270428053911425</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>1781982845.335931</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>9.253509044647217</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0.7393569946289062</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H20" s="2" t="inlineStr"/>
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R20" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S20" s="2" t="n">
+        <v>43465</v>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>0.7393569946289062</v>
+      </c>
+      <c r="U20" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad1c1013c02063c03063c0406d217</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="n">
+        <v>0.2066173944998417</v>
+      </c>
+      <c r="AM20" s="2" t="n">
+        <v>0.09371396868808718</v>
+      </c>
+      <c r="AN20" s="2" t="n">
+        <v>0.2243002432668169</v>
+      </c>
+      <c r="AO20" s="2" t="n">
+        <v>0.288976889455195</v>
+      </c>
+      <c r="AP20" s="2" t="n">
+        <v>0.1863915040900591</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>1781982845.486493</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>9.404071092605591</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>0.150562047958374</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P21" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R21" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S21" s="2" t="n">
+        <v>13911</v>
+      </c>
+      <c r="T21" s="2" t="n">
+        <v>0.150562047958374</v>
+      </c>
+      <c r="U21" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF21" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG21" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI21" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d2c1810000eac6</t>
+        </is>
+      </c>
+      <c r="AJ21" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK21" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL21" s="2" t="n">
+        <v>0.1629743605174689</v>
+      </c>
+      <c r="AM21" s="2" t="n">
+        <v>0.08856277834542516</v>
+      </c>
+      <c r="AN21" s="2" t="n">
+        <v>0.321899056220757</v>
+      </c>
+      <c r="AO21" s="2" t="n">
+        <v>0.1994973402596991</v>
+      </c>
+      <c r="AP21" s="2" t="n">
+        <v>0.22706646465665</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>1781982846.350432</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>10.26800990104675</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>0.8639388084411621</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R22" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S22" s="2" t="n">
+        <v>27235</v>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>0.8639388084411621</v>
+      </c>
+      <c r="U22" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad2c2013c02063c03063c04061054</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>0.2066450251148823</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <v>0.09376303396099886</v>
+      </c>
+      <c r="AN22" s="2" t="n">
+        <v>0.2242541246728113</v>
+      </c>
+      <c r="AO22" s="2" t="n">
+        <v>0.2889509733935218</v>
+      </c>
+      <c r="AP22" s="2" t="n">
+        <v>0.1863868428577857</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>1781982846.402136</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>10.31971406936646</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>0.05170416831970215</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P23" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q23" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R23" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S23" s="2" t="n">
+        <v>3178</v>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>0.05170416831970215</v>
+      </c>
+      <c r="U23" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d3c2810000adef</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="n">
+        <v>0.1629614710327829</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <v>0.08854330054411276</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>0.3219384575389662</v>
+      </c>
+      <c r="AO23" s="2" t="n">
+        <v>0.1994688211550626</v>
+      </c>
+      <c r="AP23" s="2" t="n">
+        <v>0.2270879497290755</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>1781982847.38401</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>11.30158805847168</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0.9818739891052246</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P24" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q24" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R24" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S24" s="2" t="n">
+        <v>65502</v>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>0.9818739891052246</v>
+      </c>
+      <c r="U24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad3c3013c02063c03063c040679ae</t>
+        </is>
+      </c>
+      <c r="AJ24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="n">
+        <v>0.2066741935101644</v>
+      </c>
+      <c r="AM24" s="2" t="n">
+        <v>0.09381563173199496</v>
+      </c>
+      <c r="AN24" s="2" t="n">
+        <v>0.2242108095324877</v>
+      </c>
+      <c r="AO24" s="2" t="n">
+        <v>0.2889119471242397</v>
+      </c>
+      <c r="AP24" s="2" t="n">
+        <v>0.1863874181011131</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>1781982847.441424</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>11.35900187492371</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0.05741381645202637</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q25" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R25" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S25" s="2" t="n">
+        <v>13974</v>
+      </c>
+      <c r="T25" s="2" t="n">
+        <v>0.05741381645202637</v>
+      </c>
+      <c r="U25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF25" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG25" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH25" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI25" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d4c381000057c4</t>
+        </is>
+      </c>
+      <c r="AJ25" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK25" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL25" s="2" t="n">
+        <v>0.1629612971044286</v>
+      </c>
+      <c r="AM25" s="2" t="n">
+        <v>0.08854187417225329</v>
+      </c>
+      <c r="AN25" s="2" t="n">
+        <v>0.3219383060455862</v>
+      </c>
+      <c r="AO25" s="2" t="n">
+        <v>0.199466364399117</v>
+      </c>
+      <c r="AP25" s="2" t="n">
+        <v>0.227092158278615</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>1781982848.431535</v>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>12.34911298751831</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>0.9901111125946045</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R26" s="2" t="n">
+        <v>254</v>
+      </c>
+      <c r="S26" s="2" t="n">
+        <v>58255</v>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>0.9901111125946045</v>
+      </c>
+      <c r="U26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad4c4013c02063c03063c040694d3</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <v>0.2066790922327139</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <v>0.09381779322787909</v>
+      </c>
+      <c r="AN26" s="2" t="n">
+        <v>0.224205832798776</v>
+      </c>
+      <c r="AO26" s="2" t="n">
+        <v>0.2889082388276489</v>
+      </c>
+      <c r="AP26" s="2" t="n">
+        <v>0.186389042912982</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>1781982848.70168</v>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>12.61925792694092</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>0.2701449394226074</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P27" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q27" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R27" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S27" s="2" t="n">
+        <v>51337</v>
+      </c>
+      <c r="T27" s="2" t="n">
+        <v>0.2701449394226074</v>
+      </c>
+      <c r="U27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF27" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG27" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH27" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI27" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d5c48100003b31</t>
+        </is>
+      </c>
+      <c r="AJ27" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK27" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL27" s="2" t="n">
+        <v>0.1629781927601491</v>
+      </c>
+      <c r="AM27" s="2" t="n">
+        <v>0.08858863191374079</v>
+      </c>
+      <c r="AN27" s="2" t="n">
+        <v>0.3218565756569251</v>
+      </c>
+      <c r="AO27" s="2" t="n">
+        <v>0.1994983663363477</v>
+      </c>
+      <c r="AP27" s="2" t="n">
+        <v>0.2270782333328372</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>1781982849.44669</v>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>13.3642680644989</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>0.7450101375579834</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P28" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q28" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R28" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S28" s="2" t="n">
+        <v>31248</v>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>0.7450101375579834</v>
+      </c>
+      <c r="U28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad5c5013c02063c03063c0406fd29</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>0.2066114048908925</v>
+      </c>
+      <c r="AM28" s="2" t="n">
+        <v>0.09372202228588421</v>
+      </c>
+      <c r="AN28" s="2" t="n">
+        <v>0.2243227382664878</v>
+      </c>
+      <c r="AO28" s="2" t="n">
+        <v>0.2889198653942944</v>
+      </c>
+      <c r="AP28" s="2" t="n">
+        <v>0.1864239691624412</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>1781982849.618694</v>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>13.5362720489502</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>0.1720039844512939</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P29" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q29" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R29" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S29" s="2" t="n">
+        <v>25025</v>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>0.1720039844512939</v>
+      </c>
+      <c r="U29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d6c5810000d996</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>0.1629581540818157</v>
+      </c>
+      <c r="AM29" s="2" t="n">
+        <v>0.08856298812362433</v>
+      </c>
+      <c r="AN29" s="2" t="n">
+        <v>0.3219164210451994</v>
+      </c>
+      <c r="AO29" s="2" t="n">
+        <v>0.1994648937291801</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>0.2270975430201803</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>1781982850.461893</v>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>14.37947106361389</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>0.8431990146636963</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O30" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P30" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q30" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R30" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S30" s="2" t="n">
+        <v>13990</v>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>0.8431990146636963</v>
+      </c>
+      <c r="U30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad6c6013c02063c03063c04063f6a</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="n">
+        <v>0.2066336456279964</v>
+      </c>
+      <c r="AM30" s="2" t="n">
+        <v>0.09375998500489456</v>
+      </c>
+      <c r="AN30" s="2" t="n">
+        <v>0.2242859080490605</v>
+      </c>
+      <c r="AO30" s="2" t="n">
+        <v>0.288900123967522</v>
+      </c>
+      <c r="AP30" s="2" t="n">
+        <v>0.1864203373505265</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>1781982850.535522</v>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>14.45309996604919</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>0.07362890243530273</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O31" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P31" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q31" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R31" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S31" s="2" t="n">
+        <v>14290</v>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>0.07362890243530273</v>
+      </c>
+      <c r="U31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d7c68100009ebf</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>0.1629440089849751</v>
+      </c>
+      <c r="AM31" s="2" t="n">
+        <v>0.08854245118020249</v>
+      </c>
+      <c r="AN31" s="2" t="n">
+        <v>0.3219593932166741</v>
+      </c>
+      <c r="AO31" s="2" t="n">
+        <v>0.1994355656976336</v>
+      </c>
+      <c r="AP31" s="2" t="n">
+        <v>0.2271185809205148</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>1781982851.494032</v>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>15.41160988807678</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>0.9585099220275879</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P32" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q32" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R32" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S32" s="2" t="n">
+        <v>7766</v>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>0.9585099220275879</v>
+      </c>
+      <c r="U32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad7c7013c02063c03063c04065690</t>
+        </is>
+      </c>
+      <c r="AJ32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL32" s="2" t="n">
+        <v>0.2066617270961306</v>
+      </c>
+      <c r="AM32" s="2" t="n">
+        <v>0.09381025977273649</v>
+      </c>
+      <c r="AN32" s="2" t="n">
+        <v>0.2242433949095372</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>0.2888645784211216</v>
+      </c>
+      <c r="AP32" s="2" t="n">
+        <v>0.1864200398004741</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>1781982851.762544</v>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>15.68012189865112</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>0.2685120105743408</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O33" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P33" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q33" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R33" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S33" s="2" t="n">
+        <v>13593</v>
+      </c>
+      <c r="T33" s="2" t="n">
+        <v>0.2685120105743408</v>
+      </c>
+      <c r="U33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF33" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG33" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH33" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d8c78100002dc1</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK33" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>0.1629757160379647</v>
+      </c>
+      <c r="AM33" s="2" t="n">
+        <v>0.08858144844748966</v>
+      </c>
+      <c r="AN33" s="2" t="n">
+        <v>0.3218623011868424</v>
+      </c>
+      <c r="AO33" s="2" t="n">
+        <v>0.1994866621519676</v>
+      </c>
+      <c r="AP33" s="2" t="n">
+        <v>0.2270938721757355</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>1781982852.496567</v>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>16.41414499282837</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>0.7340230941772461</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P34" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q34" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R34" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S34" s="2" t="n">
+        <v>36394</v>
+      </c>
+      <c r="T34" s="2" t="n">
+        <v>0.7340230941772461</v>
+      </c>
+      <c r="U34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH34" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad8c8013c02063c03063c0406e591</t>
+        </is>
+      </c>
+      <c r="AJ34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK34" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL34" s="2" t="n">
+        <v>0.2066179824739429</v>
+      </c>
+      <c r="AM34" s="2" t="n">
+        <v>0.09371239173947829</v>
+      </c>
+      <c r="AN34" s="2" t="n">
+        <v>0.2243204902376483</v>
+      </c>
+      <c r="AO34" s="2" t="n">
+        <v>0.2889199717922249</v>
+      </c>
+      <c r="AP34" s="2" t="n">
+        <v>0.1864291637567057</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="C35" s="2" t="n">
+        <v>1781982852.698985</v>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>16.61656308174133</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>0.2024180889129639</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P35" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q35" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R35" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S35" s="2" t="n">
+        <v>13230</v>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>0.2024180889129639</v>
+      </c>
+      <c r="U35" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0d9c88100006ec1</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>0.162961413765218</v>
+      </c>
+      <c r="AM35" s="2" t="n">
+        <v>0.08856296720034602</v>
+      </c>
+      <c r="AN35" s="2" t="n">
+        <v>0.3219047607648999</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>0.1994625380538051</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>0.227108320215731</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C36" s="2" t="n">
+        <v>1781982853.54497</v>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>17.46254801750183</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>0.845984935760498</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P36" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q36" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R36" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S36" s="2" t="n">
+        <v>58918</v>
+      </c>
+      <c r="T36" s="2" t="n">
+        <v>0.845984935760498</v>
+      </c>
+      <c r="U36" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X36" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH36" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ad9c9013c02063c03063c04068c6b</t>
+        </is>
+      </c>
+      <c r="AJ36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK36" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>0.2066429464297433</v>
+      </c>
+      <c r="AM36" s="2" t="n">
+        <v>0.09375567559859443</v>
+      </c>
+      <c r="AN36" s="2" t="n">
+        <v>0.2242786998647124</v>
+      </c>
+      <c r="AO36" s="2" t="n">
+        <v>0.2888979730354844</v>
+      </c>
+      <c r="AP36" s="2" t="n">
+        <v>0.1864247050714655</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="C37" s="2" t="n">
+        <v>1781982853.617083</v>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>17.53466105461121</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>0.072113037109375</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P37" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q37" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R37" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S37" s="2" t="n">
+        <v>36198</v>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>0.072113037109375</v>
+      </c>
+      <c r="U37" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0dac98100008c66</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>0.1629417192851552</v>
+      </c>
+      <c r="AM37" s="2" t="n">
+        <v>0.08853541236753192</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>0.3219645512728333</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>0.1994239460916741</v>
+      </c>
+      <c r="AP37" s="2" t="n">
+        <v>0.2271343709828056</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="C38" s="2" t="n">
+        <v>1781982854.580147</v>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>18.49772500991821</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>0.9630639553070068</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P38" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q38" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R38" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S38" s="2" t="n">
+        <v>9024</v>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>0.9630639553070068</v>
+      </c>
+      <c r="U38" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH38" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35adaca013c02063c03063c04064e28</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>0.2066715086714186</v>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>0.09380693642846258</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>0.2242355771898432</v>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>0.2888614490475435</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>0.1864245286627323</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>1781982854.846341</v>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>18.76391887664795</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>0.2661938667297363</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P39" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q39" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R39" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S39" s="2" t="n">
+        <v>41725</v>
+      </c>
+      <c r="T39" s="2" t="n">
+        <v>0.2661938667297363</v>
+      </c>
+      <c r="U39" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X39" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF39" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG39" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH39" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0dbca810000cb4f</t>
+        </is>
+      </c>
+      <c r="AJ39" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK39" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>0.1629730729999265</v>
+      </c>
+      <c r="AM39" s="2" t="n">
+        <v>0.08857403660729084</v>
+      </c>
+      <c r="AN39" s="2" t="n">
+        <v>0.3218685065912658</v>
+      </c>
+      <c r="AO39" s="2" t="n">
+        <v>0.1994746508624349</v>
+      </c>
+      <c r="AP39" s="2" t="n">
+        <v>0.2271097329390821</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="C40" s="2" t="n">
+        <v>1781982855.630035</v>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>19.54761290550232</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>0.7836940288543701</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P40" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q40" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R40" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S40" s="2" t="n">
+        <v>18540</v>
+      </c>
+      <c r="T40" s="2" t="n">
+        <v>0.7836940288543701</v>
+      </c>
+      <c r="U40" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X40" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH40" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35adbcb013c02063c03063c040627d2</t>
+        </is>
+      </c>
+      <c r="AJ40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK40" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL40" s="2" t="n">
+        <v>0.2066363051692881</v>
+      </c>
+      <c r="AM40" s="2" t="n">
+        <v>0.09372615454392104</v>
+      </c>
+      <c r="AN40" s="2" t="n">
+        <v>0.2242965079055808</v>
+      </c>
+      <c r="AO40" s="2" t="n">
+        <v>0.2889105074598334</v>
+      </c>
+      <c r="AP40" s="2" t="n">
+        <v>0.1864305249213768</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C41" s="2" t="n">
+        <v>1781982855.767176</v>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>19.68475389480591</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>0.1371409893035889</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P41" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q41" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R41" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S41" s="2" t="n">
+        <v>36205</v>
+      </c>
+      <c r="T41" s="2" t="n">
+        <v>0.1371409893035889</v>
+      </c>
+      <c r="U41" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X41" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF41" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG41" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH41" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI41" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0dccb8100003164</t>
+        </is>
+      </c>
+      <c r="AJ41" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK41" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL41" s="2" t="n">
+        <v>0.1629484450179751</v>
+      </c>
+      <c r="AM41" s="2" t="n">
+        <v>0.0885422805751265</v>
+      </c>
+      <c r="AN41" s="2" t="n">
+        <v>0.321942377440195</v>
+      </c>
+      <c r="AO41" s="2" t="n">
+        <v>0.1994327546646607</v>
+      </c>
+      <c r="AP41" s="2" t="n">
+        <v>0.2271341423020428</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="C42" s="2" t="n">
+        <v>1781982856.679816</v>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>20.59739398956299</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>0.9126400947570801</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P42" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q42" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R42" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S42" s="2" t="n">
+        <v>42084</v>
+      </c>
+      <c r="T42" s="2" t="n">
+        <v>0.9126400947570801</v>
+      </c>
+      <c r="U42" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X42" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH42" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI42" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35adccc013c02063c03063c0406caaf</t>
+        </is>
+      </c>
+      <c r="AJ42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK42" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>0.2066660864411853</v>
+      </c>
+      <c r="AM42" s="2" t="n">
+        <v>0.09377958447163108</v>
+      </c>
+      <c r="AN42" s="2" t="n">
+        <v>0.2242489508481877</v>
+      </c>
+      <c r="AO42" s="2" t="n">
+        <v>0.2888776581849452</v>
+      </c>
+      <c r="AP42" s="2" t="n">
+        <v>0.1864277200540508</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="C43" s="2" t="n">
+        <v>1781982856.751862</v>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>20.66944003105164</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>0.07204604148864746</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P43" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q43" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R43" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S43" s="2" t="n">
+        <v>24343</v>
+      </c>
+      <c r="T43" s="2" t="n">
+        <v>0.07204604148864746</v>
+      </c>
+      <c r="U43" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X43" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG43" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH43" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0ddcc8100005d91</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK43" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL43" s="2" t="n">
+        <v>0.16293955017669</v>
+      </c>
+      <c r="AM43" s="2" t="n">
+        <v>0.08852849274907762</v>
+      </c>
+      <c r="AN43" s="2" t="n">
+        <v>0.3219692907702713</v>
+      </c>
+      <c r="AO43" s="2" t="n">
+        <v>0.1994124827621021</v>
+      </c>
+      <c r="AP43" s="2" t="n">
+        <v>0.2271501835418589</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" s="2" t="n">
+        <v>1781982857.698836</v>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>21.61641407012939</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>0.9469740390777588</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R44" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S44" s="2" t="n">
+        <v>51860</v>
+      </c>
+      <c r="T44" s="2" t="n">
+        <v>0.9469740390777588</v>
+      </c>
+      <c r="U44" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X44" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI44" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35addcd013c02063c03063c0406a355</t>
+        </is>
+      </c>
+      <c r="AJ44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK44" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>0.206676659093776</v>
+      </c>
+      <c r="AM44" s="2" t="n">
+        <v>0.09379372422802001</v>
+      </c>
+      <c r="AN44" s="2" t="n">
+        <v>0.2242348900359563</v>
+      </c>
+      <c r="AO44" s="2" t="n">
+        <v>0.288865726280259</v>
+      </c>
+      <c r="AP44" s="2" t="n">
+        <v>0.1864290003619885</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C45" s="2" t="n">
+        <v>1781982857.961981</v>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>21.87955904006958</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>0.2631449699401855</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P45" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q45" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R45" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S45" s="2" t="n">
+        <v>47243</v>
+      </c>
+      <c r="T45" s="2" t="n">
+        <v>0.2631449699401855</v>
+      </c>
+      <c r="U45" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X45" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF45" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG45" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH45" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0decd810000bf36</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK45" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL45" s="2" t="n">
+        <v>0.1629702501963198</v>
+      </c>
+      <c r="AM45" s="2" t="n">
+        <v>0.08856636734640308</v>
+      </c>
+      <c r="AN45" s="2" t="n">
+        <v>0.3218752272450934</v>
+      </c>
+      <c r="AO45" s="2" t="n">
+        <v>0.1994622870715568</v>
+      </c>
+      <c r="AP45" s="2" t="n">
+        <v>0.227125868140627</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C46" s="2" t="n">
+        <v>1781982858.733556</v>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>22.65113401412964</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>0.7715749740600586</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P46" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q46" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R46" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S46" s="2" t="n">
+        <v>2986</v>
+      </c>
+      <c r="T46" s="2" t="n">
+        <v>0.7715749740600586</v>
+      </c>
+      <c r="U46" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X46" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG46" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH46" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35adece013c02063c03063c04066116</t>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK46" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>0.206642741803525</v>
+      </c>
+      <c r="AM46" s="2" t="n">
+        <v>0.09371579869966047</v>
+      </c>
+      <c r="AN46" s="2" t="n">
+        <v>0.2242945356691058</v>
+      </c>
+      <c r="AO46" s="2" t="n">
+        <v>0.2889111976922795</v>
+      </c>
+      <c r="AP46" s="2" t="n">
+        <v>0.1864357261354293</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2" t="n">
+        <v>1781982858.900537</v>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>22.81811499595642</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>0.1669809818267822</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P47" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q47" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R47" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S47" s="2" t="n">
+        <v>52776</v>
+      </c>
+      <c r="T47" s="2" t="n">
+        <v>0.1669809818267822</v>
+      </c>
+      <c r="U47" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X47" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF47" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG47" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH47" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI47" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0dfce810000f81f</t>
+        </is>
+      </c>
+      <c r="AJ47" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK47" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL47" s="2" t="n">
+        <v>0.1629509282261324</v>
+      </c>
+      <c r="AM47" s="2" t="n">
+        <v>0.08854145948634019</v>
+      </c>
+      <c r="AN47" s="2" t="n">
+        <v>0.321932923160259</v>
+      </c>
+      <c r="AO47" s="2" t="n">
+        <v>0.1994295794910504</v>
+      </c>
+      <c r="AP47" s="2" t="n">
+        <v>0.227145109636218</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C48" s="2" t="n">
+        <v>1781982859.762048</v>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>23.67962598800659</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>0.8615109920501709</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P48" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q48" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R48" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S48" s="2" t="n">
+        <v>25258</v>
+      </c>
+      <c r="T48" s="2" t="n">
+        <v>0.8615109920501709</v>
+      </c>
+      <c r="U48" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X48" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH48" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35adfcf013c02063c03063c040608ec</t>
+        </is>
+      </c>
+      <c r="AJ48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK48" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL48" s="2" t="n">
+        <v>0.2066637970161222</v>
+      </c>
+      <c r="AM48" s="2" t="n">
+        <v>0.09375128959030576</v>
+      </c>
+      <c r="AN48" s="2" t="n">
+        <v>0.224260671730146</v>
+      </c>
+      <c r="AO48" s="2" t="n">
+        <v>0.2888910146283697</v>
+      </c>
+      <c r="AP48" s="2" t="n">
+        <v>0.1864332270350563</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>1781982859.800826</v>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>23.71840405464172</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>0.03877806663513184</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P49" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q49" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R49" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S49" s="2" t="n">
+        <v>6515</v>
+      </c>
+      <c r="T49" s="2" t="n">
+        <v>0.03877806663513184</v>
+      </c>
+      <c r="U49" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X49" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF49" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG49" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH49" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI49" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0e0cf81000084d3</t>
+        </is>
+      </c>
+      <c r="AJ49" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK49" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL49" s="2" t="n">
+        <v>0.1629174713737379</v>
+      </c>
+      <c r="AM49" s="2" t="n">
+        <v>0.0885215768442298</v>
+      </c>
+      <c r="AN49" s="2" t="n">
+        <v>0.3220055277136878</v>
+      </c>
+      <c r="AO49" s="2" t="n">
+        <v>0.1993701919249938</v>
+      </c>
+      <c r="AP49" s="2" t="n">
+        <v>0.2271852321433505</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>1781982860.780011</v>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>24.69758892059326</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>0.9791848659515381</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P50" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q50" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R50" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S50" s="2" t="n">
+        <v>48308</v>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>0.9791848659515381</v>
+      </c>
+      <c r="U50" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X50" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH50" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI50" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ae0c0013c02063c03063c0406adc7</t>
+        </is>
+      </c>
+      <c r="AJ50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK50" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL50" s="2" t="n">
+        <v>0.206692808851681</v>
+      </c>
+      <c r="AM50" s="2" t="n">
+        <v>0.09380367581660048</v>
+      </c>
+      <c r="AN50" s="2" t="n">
+        <v>0.2242174430793751</v>
+      </c>
+      <c r="AO50" s="2" t="n">
+        <v>0.2888524252540204</v>
+      </c>
+      <c r="AP50" s="2" t="n">
+        <v>0.1864336469983231</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>1781982861.059294</v>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>24.97687196731567</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>0.2792830467224121</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P51" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q51" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R51" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S51" s="2" t="n">
+        <v>6166</v>
+      </c>
+      <c r="T51" s="2" t="n">
+        <v>0.2792830467224121</v>
+      </c>
+      <c r="U51" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X51" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF51" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG51" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH51" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI51" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0e1c0810000c7d3</t>
+        </is>
+      </c>
+      <c r="AJ51" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK51" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL51" s="2" t="n">
+        <v>0.1629550268417137</v>
+      </c>
+      <c r="AM51" s="2" t="n">
+        <v>0.08856873521096338</v>
+      </c>
+      <c r="AN51" s="2" t="n">
+        <v>0.3218903704997401</v>
+      </c>
+      <c r="AO51" s="2" t="n">
+        <v>0.1994329250615433</v>
+      </c>
+      <c r="AP51" s="2" t="n">
+        <v>0.2271529423860396</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>1781982861.796548</v>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>25.71412587165833</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>0.7372539043426514</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P52" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q52" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R52" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S52" s="2" t="n">
+        <v>42260</v>
+      </c>
+      <c r="T52" s="2" t="n">
+        <v>0.7372539043426514</v>
+      </c>
+      <c r="U52" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X52" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG52" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH52" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI52" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ae1c1013c02063c03063c0406c43d</t>
+        </is>
+      </c>
+      <c r="AJ52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK52" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL52" s="2" t="n">
+        <v>0.2066449161170725</v>
+      </c>
+      <c r="AM52" s="2" t="n">
+        <v>0.09369703274392467</v>
+      </c>
+      <c r="AN52" s="2" t="n">
+        <v>0.2243005456194328</v>
+      </c>
+      <c r="AO52" s="2" t="n">
+        <v>0.2889150785291417</v>
+      </c>
+      <c r="AP52" s="2" t="n">
+        <v>0.1864424269904284</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>1781982861.995647</v>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>25.91322493553162</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>0.199099063873291</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr"/>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P53" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q53" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R53" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S53" s="2" t="n">
+        <v>30350</v>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>0.199099063873291</v>
+      </c>
+      <c r="U53" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X53" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF53" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG53" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH53" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI53" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0e2c18100002574</t>
+        </is>
+      </c>
+      <c r="AJ53" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK53" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL53" s="2" t="n">
+        <v>0.1629376175477286</v>
+      </c>
+      <c r="AM53" s="2" t="n">
+        <v>0.08854659106767282</v>
+      </c>
+      <c r="AN53" s="2" t="n">
+        <v>0.3219421162241868</v>
+      </c>
+      <c r="AO53" s="2" t="n">
+        <v>0.1994042477484447</v>
+      </c>
+      <c r="AP53" s="2" t="n">
+        <v>0.2271694274119672</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>1781982862.845817</v>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>26.76339507102966</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>0.8501701354980469</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P54" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q54" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R54" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S54" s="2" t="n">
+        <v>25002</v>
+      </c>
+      <c r="T54" s="2" t="n">
+        <v>0.8501701354980469</v>
+      </c>
+      <c r="U54" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X54" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH54" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI54" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ae2c2013c02063c03063c0406067e</t>
+        </is>
+      </c>
+      <c r="AJ54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK54" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL54" s="2" t="n">
+        <v>0.2066701613986962</v>
+      </c>
+      <c r="AM54" s="2" t="n">
+        <v>0.09374089333968934</v>
+      </c>
+      <c r="AN54" s="2" t="n">
+        <v>0.2242584319030799</v>
+      </c>
+      <c r="AO54" s="2" t="n">
+        <v>0.2888924587641192</v>
+      </c>
+      <c r="AP54" s="2" t="n">
+        <v>0.1864380545944155</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>1781982862.91451</v>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>26.83208799362183</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>0.06869292259216309</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P55" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q55" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R55" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S55" s="2" t="n">
+        <v>35879</v>
+      </c>
+      <c r="T55" s="2" t="n">
+        <v>0.06869292259216309</v>
+      </c>
+      <c r="U55" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X55" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF55" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG55" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH55" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI55" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0e3c2810000625d</t>
+        </is>
+      </c>
+      <c r="AJ55" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK55" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL55" s="2" t="n">
+        <v>0.1629181651390816</v>
+      </c>
+      <c r="AM55" s="2" t="n">
+        <v>0.08851924606704983</v>
+      </c>
+      <c r="AN55" s="2" t="n">
+        <v>0.3220011838232565</v>
+      </c>
+      <c r="AO55" s="2" t="n">
+        <v>0.1993658150509946</v>
+      </c>
+      <c r="AP55" s="2" t="n">
+        <v>0.2271955899196175</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>1781982863.880696</v>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>27.79827404022217</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>0.9661860466003418</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P56" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q56" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R56" s="2" t="n">
+        <v>253</v>
+      </c>
+      <c r="S56" s="2" t="n">
+        <v>63353</v>
+      </c>
+      <c r="T56" s="2" t="n">
+        <v>0.9661860466003418</v>
+      </c>
+      <c r="U56" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X56" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD56" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH56" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI56" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ae3c3013c02063c03063c04066f84</t>
+        </is>
+      </c>
+      <c r="AJ56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK56" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL56" s="2" t="n">
+        <v>0.2066985801604556</v>
+      </c>
+      <c r="AM56" s="2" t="n">
+        <v>0.0937918700902397</v>
+      </c>
+      <c r="AN56" s="2" t="n">
+        <v>0.2242157026057654</v>
+      </c>
+      <c r="AO56" s="2" t="n">
+        <v>0.2888558160987927</v>
+      </c>
+      <c r="AP56" s="2" t="n">
+        <v>0.1864380310447468</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>1781982864.143442</v>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>28.06101989746094</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>0.2627458572387695</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P57" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q57" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R57" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S57" s="2" t="n">
+        <v>29127</v>
+      </c>
+      <c r="T57" s="2" t="n">
+        <v>0.2627458572387695</v>
+      </c>
+      <c r="U57" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X57" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD57" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF57" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG57" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH57" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI57" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0e4c38100009876</t>
+        </is>
+      </c>
+      <c r="AJ57" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK57" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL57" s="2" t="n">
+        <v>0.1629491313866546</v>
+      </c>
+      <c r="AM57" s="2" t="n">
+        <v>0.08855752203196854</v>
+      </c>
+      <c r="AN57" s="2" t="n">
+        <v>0.3219062778466344</v>
+      </c>
+      <c r="AO57" s="2" t="n">
+        <v>0.1994162299302678</v>
+      </c>
+      <c r="AP57" s="2" t="n">
+        <v>0.2271708388044747</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>1781982864.93166</v>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>28.84923791885376</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>0.7882180213928223</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="P58" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q58" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="R58" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S58" s="2" t="n">
+        <v>58075</v>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>0.7882180213928223</v>
+      </c>
+      <c r="U58" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="X58" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="Y58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="2" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="AH58" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI58" s="2" t="inlineStr">
+        <is>
+          <t>056411c401000200c35ae4c4013c02063c03063c040682f9</t>
+        </is>
+      </c>
+      <c r="AJ58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK58" s="2" t="inlineStr">
+        <is>
+          <t>REPLAY_ATTACK</t>
+        </is>
+      </c>
+      <c r="AL58" s="2" t="n">
+        <v>0.2066448442147548</v>
+      </c>
+      <c r="AM58" s="2" t="n">
+        <v>0.09372464650535918</v>
+      </c>
+      <c r="AN58" s="2" t="n">
+        <v>0.2243089130595894</v>
+      </c>
+      <c r="AO58" s="2" t="n">
+        <v>0.2888508786887422</v>
+      </c>
+      <c r="AP58" s="2" t="n">
+        <v>0.1864707175315545</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>live_capture</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>1781982865.066991</v>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>28.98456907272339</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>0.1353311538696289</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>127.0.0.1</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>128</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>20003</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>65130</v>
+      </c>
+      <c r="P59" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q59" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="R59" s="2" t="n">
+        <v>252</v>
+      </c>
+      <c r="S59" s="2" t="n">
+        <v>25409</v>
+      </c>
+      <c r="T59" s="2" t="n">
+        <v>0.1353311538696289</v>
+      </c>
+      <c r="U59" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>0x0564</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="X59" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="Y59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF59" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AG59" s="2" t="inlineStr">
+        <is>
+          <t>RESPONSE</t>
+        </is>
+      </c>
+      <c r="AH59" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI59" s="2" t="inlineStr">
+        <is>
+          <t>05640a440200010010f0e5c4810000f483</t>
+        </is>
+      </c>
+      <c r="AJ59" s="2" t="n">
+        <v>129</v>
+      </c>
+      <c r="AK59" s="2" t="inlineStr">
+        <is>
+          <t>DNP3_RECON</t>
+        </is>
+      </c>
+      <c r="AL59" s="2" t="n">
+        <v>0.1629249947299674</v>
+      </c>
+      <c r="AM59" s="2" t="n">
+        <v>0.08852631051749639</v>
+      </c>
+      <c r="AN59" s="2" t="n">
+        <v>0.3219786594556183</v>
+      </c>
+      <c r="AO59" s="2" t="n">
+        <v>0.1993749490269935</v>
+      </c>
+      <c r="AP59" s="2" t="n">
+        <v>0.2271950862699244</v>
       </c>
     </row>
   </sheetData>
